--- a/operaciones.xlsx
+++ b/operaciones.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29910"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD0E7901-79FA-4A07-BC95-6B301E9ADDEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{291293E0-D776-408F-9700-73D630258304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="55">
   <si>
     <t>Fecha</t>
   </si>
@@ -1271,7 +1271,21 @@
       </c>
     </row>
     <row r="25" spans="1:21">
-      <c r="A25" s="1"/>
+      <c r="A25" s="1">
+        <v>45914</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25">
+        <v>5000</v>
+      </c>
       <c r="I25">
         <f>+I21+I20-I17</f>
         <v>12330</v>

--- a/operaciones.xlsx
+++ b/operaciones.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29910"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{291293E0-D776-408F-9700-73D630258304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{729ED3DD-665D-4071-9371-B9595139D59E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Operaciones" sheetId="1" r:id="rId1"/>
@@ -209,10 +209,17 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -238,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -246,6 +253,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1391,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8AE11B3-0E9A-43BD-8421-E8F835D75104}">
-  <dimension ref="A1:Z248"/>
+  <dimension ref="A1:Z250"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.85546875" customWidth="1"/>
@@ -20445,6 +20454,166 @@
         <v>65.67</v>
       </c>
     </row>
+    <row r="249" spans="1:26" s="6" customFormat="1">
+      <c r="A249" s="5">
+        <v>46098</v>
+      </c>
+      <c r="B249" s="6">
+        <v>60.5</v>
+      </c>
+      <c r="C249" s="6">
+        <v>58.08</v>
+      </c>
+      <c r="D249" s="6">
+        <v>57.62</v>
+      </c>
+      <c r="E249" s="6">
+        <v>62.3</v>
+      </c>
+      <c r="F249" s="6">
+        <v>54.6</v>
+      </c>
+      <c r="G249" s="6">
+        <v>55</v>
+      </c>
+      <c r="H249" s="6">
+        <v>58</v>
+      </c>
+      <c r="I249" s="6">
+        <v>54.84</v>
+      </c>
+      <c r="J249" s="6">
+        <v>54.32</v>
+      </c>
+      <c r="K249" s="6">
+        <v>55.98</v>
+      </c>
+      <c r="L249" s="6">
+        <v>45</v>
+      </c>
+      <c r="M249" s="6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="N249" s="6">
+        <v>97.6</v>
+      </c>
+      <c r="O249" s="6">
+        <v>91.5</v>
+      </c>
+      <c r="P249" s="6">
+        <v>89.92</v>
+      </c>
+      <c r="Q249" s="6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R249" s="6">
+        <v>101.9</v>
+      </c>
+      <c r="S249" s="6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T249" s="6">
+        <v>94.99</v>
+      </c>
+      <c r="U249" s="6">
+        <v>90.17</v>
+      </c>
+      <c r="V249" s="6">
+        <v>87.83</v>
+      </c>
+      <c r="W249" s="6">
+        <v>0</v>
+      </c>
+      <c r="X249" s="6">
+        <v>99.94</v>
+      </c>
+      <c r="Y249" s="6">
+        <v>67.040000000000006</v>
+      </c>
+      <c r="Z249" s="6">
+        <v>65.67</v>
+      </c>
+    </row>
+    <row r="250" spans="1:26" s="6" customFormat="1">
+      <c r="A250" s="5">
+        <v>46099</v>
+      </c>
+      <c r="B250" s="6">
+        <v>60.5</v>
+      </c>
+      <c r="C250" s="6">
+        <v>58.08</v>
+      </c>
+      <c r="D250" s="6">
+        <v>57.62</v>
+      </c>
+      <c r="E250" s="6">
+        <v>62.3</v>
+      </c>
+      <c r="F250" s="6">
+        <v>54.6</v>
+      </c>
+      <c r="G250" s="6">
+        <v>55</v>
+      </c>
+      <c r="H250" s="6">
+        <v>58</v>
+      </c>
+      <c r="I250" s="6">
+        <v>54.84</v>
+      </c>
+      <c r="J250" s="6">
+        <v>54.32</v>
+      </c>
+      <c r="K250" s="6">
+        <v>55.98</v>
+      </c>
+      <c r="L250" s="6">
+        <v>45</v>
+      </c>
+      <c r="M250" s="6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="N250" s="6">
+        <v>97.6</v>
+      </c>
+      <c r="O250" s="6">
+        <v>91.5</v>
+      </c>
+      <c r="P250" s="6">
+        <v>89.92</v>
+      </c>
+      <c r="Q250" s="6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R250" s="6">
+        <v>101.9</v>
+      </c>
+      <c r="S250" s="6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T250" s="6">
+        <v>94.99</v>
+      </c>
+      <c r="U250" s="6">
+        <v>90.17</v>
+      </c>
+      <c r="V250" s="6">
+        <v>87.83</v>
+      </c>
+      <c r="W250" s="6">
+        <v>0</v>
+      </c>
+      <c r="X250" s="6">
+        <v>99.94</v>
+      </c>
+      <c r="Y250" s="6">
+        <v>67.040000000000006</v>
+      </c>
+      <c r="Z250" s="6">
+        <v>65.67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/operaciones.xlsx
+++ b/operaciones.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29910"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{729ED3DD-665D-4071-9371-B9595139D59E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF465BBE-DBF6-4C17-8F60-C29B14F2B4A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Operaciones" sheetId="1" r:id="rId1"/>
@@ -589,6 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:U39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -639,7 +640,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" hidden="1">
       <c r="A2" s="1">
         <v>45581</v>
       </c>
@@ -729,7 +730,7 @@
         <v>21080</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" hidden="1">
       <c r="A5" s="1">
         <v>45978</v>
       </c>
@@ -801,7 +802,7 @@
         <v>31620</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" hidden="1">
       <c r="A8" s="1">
         <v>45665</v>
       </c>
@@ -827,7 +828,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" hidden="1">
       <c r="A9" s="1">
         <v>45665</v>
       </c>
@@ -844,7 +845,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" hidden="1">
       <c r="A10" s="1">
         <v>45665</v>
       </c>
@@ -875,7 +876,7 @@
         <v>45665</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
@@ -883,9 +884,15 @@
       <c r="D11" t="s">
         <v>15</v>
       </c>
+      <c r="E11">
+        <v>300</v>
+      </c>
+      <c r="F11">
+        <v>54</v>
+      </c>
       <c r="G11">
-        <f>1575/2</f>
-        <v>787.5</v>
+        <f>E11*F11</f>
+        <v>16200</v>
       </c>
       <c r="M11" t="s">
         <v>24</v>
@@ -894,7 +901,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" hidden="1">
       <c r="A12" s="1">
         <v>45667</v>
       </c>
@@ -921,7 +928,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" hidden="1">
       <c r="A13" s="1">
         <v>45669</v>
       </c>
@@ -945,7 +952,7 @@
         <v>68500</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" hidden="1">
       <c r="A14" s="1">
         <v>45669</v>
       </c>
@@ -969,7 +976,7 @@
         <v>68500</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" hidden="1">
       <c r="A15" s="1">
         <v>45698</v>
       </c>
@@ -997,7 +1004,7 @@
         <v>18033</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" hidden="1">
       <c r="A16" s="1">
         <v>45846</v>
       </c>
@@ -1014,7 +1021,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="17" spans="1:21">
+    <row r="17" spans="1:21" hidden="1">
       <c r="A17" s="1">
         <v>45846</v>
       </c>
@@ -1078,7 +1085,7 @@
         <v>17700</v>
       </c>
     </row>
-    <row r="20" spans="1:21">
+    <row r="20" spans="1:21" hidden="1">
       <c r="A20" s="1">
         <v>45848</v>
       </c>
@@ -1110,7 +1117,7 @@
         <v>61.7</v>
       </c>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:21" hidden="1">
       <c r="A21" s="1">
         <v>45879</v>
       </c>
@@ -1165,7 +1172,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="29.25">
+    <row r="22" spans="1:21" ht="29.25" hidden="1">
       <c r="A22" s="1">
         <v>45910</v>
       </c>
@@ -1231,7 +1238,7 @@
         <v>-1285</v>
       </c>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:21" hidden="1">
       <c r="A23" s="1">
         <v>45912</v>
       </c>
@@ -1334,14 +1341,14 @@
       <c r="A32" s="1"/>
       <c r="I32">
         <f>+G11+G18</f>
-        <v>1575</v>
+        <v>16987.5</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="1"/>
       <c r="I33">
         <f>15720-I30+I31+I32</f>
-        <v>-405</v>
+        <v>15007.5</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1373,7 +1380,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G23" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G25" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="AL41"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G17">
     <sortCondition ref="A2:A17"/>
   </sortState>

--- a/operaciones.xlsx
+++ b/operaciones.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF465BBE-DBF6-4C17-8F60-C29B14F2B4A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{50C221E3-06F0-47EC-8EAA-16FDD251454A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="58">
   <si>
     <t>Fecha</t>
   </si>
@@ -55,7 +55,13 @@
     <t>Precio</t>
   </si>
   <si>
-    <t>Valor</t>
+    <t>Valor USD</t>
+  </si>
+  <si>
+    <t>Precio ARS</t>
+  </si>
+  <si>
+    <t>Valor ARS</t>
   </si>
   <si>
     <t xml:space="preserve">Compra </t>
@@ -201,6 +207,9 @@
   <si>
     <t>BPO8C</t>
   </si>
+  <si>
+    <t>ARS</t>
+  </si>
 </sst>
 </file>
 
@@ -245,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -255,6 +264,11 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -589,8 +603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:U39"/>
+  <dimension ref="A1:U37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -599,7 +612,9 @@
     <col min="4" max="4" width="14.140625" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" customWidth="1"/>
     <col min="6" max="6" width="13.85546875" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" style="9" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" style="9" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" customWidth="1"/>
     <col min="12" max="12" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.28515625" customWidth="1"/>
     <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
@@ -627,31 +642,37 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
       <c r="M1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" hidden="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="18" customHeight="1">
       <c r="A2" s="1">
         <v>45581</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2">
         <v>1000</v>
@@ -659,18 +680,26 @@
       <c r="F2">
         <v>63.26</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="9">
         <f>+F2*E2</f>
         <v>63260</v>
       </c>
+      <c r="H2" s="8">
+        <f>F2*VLOOKUP(A2,Precios!$A$2:$AA$600,27)</f>
+        <v>72369.440000000002</v>
+      </c>
+      <c r="I2" s="8">
+        <f>G2*VLOOKUP(A2,Precios!$A$2:$AA$600,27)</f>
+        <v>72369440</v>
+      </c>
       <c r="M2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" t="s">
         <v>14</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -678,13 +707,13 @@
         <v>45581</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3">
         <v>900</v>
@@ -692,18 +721,26 @@
       <c r="F3">
         <v>52.7</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="9">
         <f>+F3*E3</f>
         <v>47430</v>
       </c>
+      <c r="H3" s="8">
+        <f>F3*VLOOKUP(A3,Precios!$A$2:$AA$600,27)</f>
+        <v>60288.800000000003</v>
+      </c>
+      <c r="I3" s="8">
+        <f>G3*VLOOKUP(A3,Precios!$A$2:$AA$600,27)</f>
+        <v>54259920</v>
+      </c>
       <c r="M3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -711,13 +748,13 @@
         <v>45585</v>
       </c>
       <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4">
         <v>400</v>
@@ -725,23 +762,31 @@
       <c r="F4">
         <v>52.7</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="9">
         <f>+F4*E4</f>
         <v>21080</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" hidden="1">
+      <c r="H4" s="8">
+        <f>F4*VLOOKUP(A4,Precios!$A$2:$AA$600,27)</f>
+        <v>60394.200000000004</v>
+      </c>
+      <c r="I4" s="8">
+        <f>G4*VLOOKUP(A4,Precios!$A$2:$AA$600,27)</f>
+        <v>24157680</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="1">
         <v>45978</v>
       </c>
       <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5">
         <v>100</v>
@@ -749,9 +794,17 @@
       <c r="F5">
         <v>50</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="9">
         <f>+F5*E5</f>
         <v>5000</v>
+      </c>
+      <c r="H5" s="8">
+        <f>F5*VLOOKUP(A5,Precios!$A$2:$AA$600,27)</f>
+        <v>68900</v>
+      </c>
+      <c r="I5" s="8">
+        <f>G5*VLOOKUP(A5,Precios!$A$2:$AA$600,27)</f>
+        <v>6890000</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -759,13 +812,13 @@
         <v>45583</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E6">
         <v>100</v>
@@ -773,9 +826,17 @@
       <c r="F6">
         <v>52.7</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="9">
         <f>+F6*E6</f>
         <v>5270</v>
+      </c>
+      <c r="H6" s="8">
+        <f>F6*VLOOKUP(A6,Precios!$A$2:$AA$600,27)</f>
+        <v>60394.200000000004</v>
+      </c>
+      <c r="I6" s="8">
+        <f>G6*VLOOKUP(A6,Precios!$A$2:$AA$600,27)</f>
+        <v>6039420</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -783,13 +844,13 @@
         <v>45584</v>
       </c>
       <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E7">
         <v>600</v>
@@ -797,78 +858,110 @@
       <c r="F7">
         <v>52.7</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="9">
         <f>+F7*E7</f>
         <v>31620</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" hidden="1">
+      <c r="H7" s="8">
+        <f>F7*VLOOKUP(A7,Precios!$A$2:$AA$600,27)</f>
+        <v>60394.200000000004</v>
+      </c>
+      <c r="I7" s="8">
+        <f>G7*VLOOKUP(A7,Precios!$A$2:$AA$600,27)</f>
+        <v>36236520</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="1">
         <v>45665</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
+        <v>14</v>
+      </c>
+      <c r="G8" s="9">
         <v>8000</v>
       </c>
+      <c r="H8" s="8">
+        <f>F8*VLOOKUP(A8,Precios!$A$2:$AA$600,27)</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="8">
+        <f>G8*VLOOKUP(A8,Precios!$A$2:$AA$600,27)</f>
+        <v>9584000</v>
+      </c>
       <c r="M8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" hidden="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="1">
         <v>45665</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9">
+        <v>20</v>
+      </c>
+      <c r="G9" s="9">
         <v>8000</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" hidden="1">
+      <c r="H9" s="8">
+        <f>F9*VLOOKUP(A9,Precios!$A$2:$AA$600,27)</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="8">
+        <f>G9*VLOOKUP(A9,Precios!$A$2:$AA$600,27)</f>
+        <v>9584000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="1">
         <v>45665</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10">
+        <v>14</v>
+      </c>
+      <c r="G10" s="9">
         <v>375</v>
       </c>
+      <c r="H10" s="8">
+        <f>F10*VLOOKUP(A10,Precios!$A$2:$AA$600,27)</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="8">
+        <f>G10*VLOOKUP(A10,Precios!$A$2:$AA$600,27)</f>
+        <v>449250</v>
+      </c>
       <c r="M10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -876,13 +969,13 @@
         <v>45665</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E11">
         <v>300</v>
@@ -890,29 +983,37 @@
       <c r="F11">
         <v>54</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="9">
         <f>E11*F11</f>
         <v>16200</v>
       </c>
+      <c r="H11" s="8">
+        <f>F11*VLOOKUP(A11,Precios!$A$2:$AA$600,27)</f>
+        <v>64692</v>
+      </c>
+      <c r="I11" s="8">
+        <f>G11*VLOOKUP(A11,Precios!$A$2:$AA$600,27)</f>
+        <v>19407600</v>
+      </c>
       <c r="M11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" hidden="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="1">
         <v>45667</v>
       </c>
       <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
         <v>13</v>
       </c>
-      <c r="C12" t="s">
-        <v>11</v>
-      </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E12">
         <v>1000</v>
@@ -920,26 +1021,34 @@
       <c r="F12">
         <v>68.5</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="9">
         <f>+F12*E12</f>
         <v>68500</v>
       </c>
+      <c r="H12" s="8">
+        <f>F12*VLOOKUP(A12,Precios!$A$2:$AA$600,27)</f>
+        <v>82200</v>
+      </c>
+      <c r="I12" s="8">
+        <f>G12*VLOOKUP(A12,Precios!$A$2:$AA$600,27)</f>
+        <v>82200000</v>
+      </c>
       <c r="M12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" hidden="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="1">
         <v>45669</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
         <v>11</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
       </c>
       <c r="E13">
         <v>1000</v>
@@ -947,23 +1056,31 @@
       <c r="F13">
         <v>68.5</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="9">
         <f>+F13*E13</f>
         <v>68500</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" hidden="1">
+      <c r="H13" s="8">
+        <f>F13*VLOOKUP(A13,Precios!$A$2:$AA$600,27)</f>
+        <v>82200</v>
+      </c>
+      <c r="I13" s="8">
+        <f>G13*VLOOKUP(A13,Precios!$A$2:$AA$600,27)</f>
+        <v>82200000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="1">
         <v>45669</v>
       </c>
       <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
         <v>13</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>11</v>
-      </c>
-      <c r="D14" t="s">
-        <v>9</v>
       </c>
       <c r="E14">
         <v>1000</v>
@@ -971,23 +1088,31 @@
       <c r="F14">
         <v>68.5</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="9">
         <f>+F14*E14</f>
         <v>68500</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" hidden="1">
+      <c r="H14" s="8">
+        <f>F14*VLOOKUP(A14,Precios!$A$2:$AA$600,27)</f>
+        <v>82200</v>
+      </c>
+      <c r="I14" s="8">
+        <f>G14*VLOOKUP(A14,Precios!$A$2:$AA$600,27)</f>
+        <v>82200000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="1">
         <v>45698</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E15">
         <v>200</v>
@@ -995,51 +1120,67 @@
       <c r="F15">
         <v>64.7</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="9">
         <f>+F15*E15</f>
         <v>12940</v>
       </c>
-      <c r="I15">
-        <f>300*60.11</f>
-        <v>18033</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" hidden="1">
+      <c r="H15" s="8">
+        <f>F15*VLOOKUP(A15,Precios!$A$2:$AA$600,27)</f>
+        <v>78998.7</v>
+      </c>
+      <c r="I15" s="8">
+        <f>G15*VLOOKUP(A15,Precios!$A$2:$AA$600,27)</f>
+        <v>15799740</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="1">
         <v>45846</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
+        <v>14</v>
+      </c>
+      <c r="G16" s="9">
         <v>1600</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" hidden="1">
+      <c r="H16" s="8">
+        <f>F16*VLOOKUP(A16,Precios!$A$2:$AA$600,27)</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="8">
+        <f>G16*VLOOKUP(A16,Precios!$A$2:$AA$600,27)</f>
+        <v>2107200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17" s="1">
         <v>45846</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17">
+        <v>14</v>
+      </c>
+      <c r="G17" s="9">
         <v>75</v>
       </c>
-      <c r="I17">
-        <f>+G2+G15+G20</f>
-        <v>112620</v>
+      <c r="H17" s="8">
+        <f>F17*VLOOKUP(A17,Precios!$A$2:$AA$600,27)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="8">
+        <f>G17*VLOOKUP(A17,Precios!$A$2:$AA$600,27)</f>
+        <v>98775</v>
       </c>
       <c r="J17" s="3"/>
     </row>
@@ -1048,17 +1189,25 @@
         <v>45846</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18">
+        <v>17</v>
+      </c>
+      <c r="G18" s="9">
         <f>1575/2</f>
         <v>787.5</v>
+      </c>
+      <c r="H18" s="8">
+        <f>F18*VLOOKUP(A18,Precios!$A$2:$AA$600,27)</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="8">
+        <f>G18*VLOOKUP(A18,Precios!$A$2:$AA$600,27)</f>
+        <v>1037137.5</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -1066,13 +1215,13 @@
         <v>45847</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E19">
         <v>300</v>
@@ -1080,23 +1229,31 @@
       <c r="F19">
         <v>59</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="9">
         <f>+F19*E19</f>
         <v>17700</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" hidden="1">
+      <c r="H19" s="8">
+        <f>F19*VLOOKUP(A19,Precios!$A$2:$AA$600,27)</f>
+        <v>77703</v>
+      </c>
+      <c r="I19" s="8">
+        <f>G19*VLOOKUP(A19,Precios!$A$2:$AA$600,27)</f>
+        <v>23310900</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
       <c r="A20" s="1">
         <v>45848</v>
       </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E20">
         <v>600</v>
@@ -1104,31 +1261,35 @@
       <c r="F20">
         <v>60.7</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="9">
         <f>+F20*E20</f>
         <v>36420</v>
       </c>
-      <c r="I20">
-        <f>+G12+G21</f>
-        <v>114900</v>
+      <c r="H20" s="8">
+        <f>F20*VLOOKUP(A20,Precios!$A$2:$AA$600,27)</f>
+        <v>80002.600000000006</v>
+      </c>
+      <c r="I20" s="8">
+        <f>G20*VLOOKUP(A20,Precios!$A$2:$AA$600,27)</f>
+        <v>48001560</v>
       </c>
       <c r="R20">
         <f>(G15+G20)/(E15+E20)</f>
         <v>61.7</v>
       </c>
     </row>
-    <row r="21" spans="1:21" hidden="1">
+    <row r="21" spans="1:21">
       <c r="A21" s="1">
         <v>45879</v>
       </c>
       <c r="B21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" t="s">
         <v>13</v>
       </c>
-      <c r="C21" t="s">
-        <v>11</v>
-      </c>
       <c r="D21" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E21">
         <v>800</v>
@@ -1136,54 +1297,58 @@
       <c r="F21">
         <v>58</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="9">
         <f>+F21*E21</f>
         <v>46400</v>
       </c>
-      <c r="I21">
-        <f>+G8+G10+G16+G17</f>
-        <v>10050</v>
+      <c r="H21" s="8">
+        <f>F21*VLOOKUP(A21,Precios!$A$2:$AA$600,27)</f>
+        <v>77662</v>
+      </c>
+      <c r="I21" s="8">
+        <f>G21*VLOOKUP(A21,Precios!$A$2:$AA$600,27)</f>
+        <v>62129600</v>
       </c>
       <c r="L21" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M21" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N21" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O21" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P21" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q21" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="R21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S21" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="T21" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" ht="29.25" hidden="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
       <c r="A22" s="1">
         <v>45910</v>
       </c>
       <c r="B22" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E22">
         <v>400</v>
@@ -1191,12 +1356,20 @@
       <c r="F22">
         <v>55</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="9">
         <f>+F22*E22</f>
         <v>22000</v>
       </c>
+      <c r="H22" s="8">
+        <f>F22*VLOOKUP(A22,Precios!$A$2:$AA$600,27)</f>
+        <v>74855</v>
+      </c>
+      <c r="I22" s="8">
+        <f>G22*VLOOKUP(A22,Precios!$A$2:$AA$600,27)</f>
+        <v>29942000</v>
+      </c>
       <c r="K22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L22">
         <f>+E15+E20-E21</f>
@@ -1238,18 +1411,18 @@
         <v>-1285</v>
       </c>
     </row>
-    <row r="23" spans="1:21" hidden="1">
+    <row r="23" spans="1:21">
       <c r="A23" s="1">
         <v>45912</v>
       </c>
       <c r="B23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" t="s">
         <v>13</v>
       </c>
-      <c r="C23" t="s">
-        <v>11</v>
-      </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E23">
         <v>200</v>
@@ -1257,9 +1430,17 @@
       <c r="F23">
         <v>54</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="9">
         <f>+F23*E23</f>
         <v>10800</v>
+      </c>
+      <c r="H23" s="8">
+        <f>F23*VLOOKUP(A23,Precios!$A$2:$AA$600,27)</f>
+        <v>73602</v>
+      </c>
+      <c r="I23" s="8">
+        <f>G23*VLOOKUP(A23,Precios!$A$2:$AA$600,27)</f>
+        <v>14720400</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -1267,13 +1448,13 @@
         <v>45913</v>
       </c>
       <c r="B24" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E24">
         <v>300</v>
@@ -1281,9 +1462,17 @@
       <c r="F24">
         <v>50</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="9">
         <f>+F24*E24</f>
         <v>15000</v>
+      </c>
+      <c r="H24" s="8">
+        <f>F24*VLOOKUP(A24,Precios!$A$2:$AA$600,27)</f>
+        <v>68150</v>
+      </c>
+      <c r="I24" s="8">
+        <f>G24*VLOOKUP(A24,Precios!$A$2:$AA$600,27)</f>
+        <v>20445000</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -1291,20 +1480,28 @@
         <v>45914</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25">
+        <v>17</v>
+      </c>
+      <c r="G25" s="9">
         <v>5000</v>
       </c>
-      <c r="I25">
-        <f>+I21+I20-I17</f>
-        <v>12330</v>
+      <c r="H25" s="8">
+        <f>F25*VLOOKUP(A25,Precios!$A$2:$AA$600,27)</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="8">
+        <f>G25*VLOOKUP(A25,Precios!$A$2:$AA$600,27)</f>
+        <v>6815000</v>
+      </c>
+      <c r="L25">
+        <f>J25+J27+J28</f>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:21">
@@ -1312,8 +1509,8 @@
     </row>
     <row r="27" spans="1:21">
       <c r="A27" s="1"/>
-      <c r="I27">
-        <f>+G13-G14</f>
+      <c r="L27">
+        <f>J30+J29+J26</f>
         <v>0</v>
       </c>
     </row>
@@ -1322,71 +1519,37 @@
     </row>
     <row r="29" spans="1:21">
       <c r="A29" s="1"/>
+      <c r="L29">
+        <f>L25-L27</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:21">
       <c r="A30" s="1"/>
-      <c r="I30">
-        <f>+G3+G6+G19</f>
-        <v>70400</v>
-      </c>
     </row>
     <row r="31" spans="1:21">
       <c r="A31" s="1"/>
-      <c r="I31">
-        <f>+G4+G7</f>
-        <v>52700</v>
-      </c>
     </row>
     <row r="32" spans="1:21">
       <c r="A32" s="1"/>
-      <c r="I32">
-        <f>+G11+G18</f>
-        <v>16987.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+    </row>
+    <row r="33" spans="1:1">
       <c r="A33" s="1"/>
-      <c r="I33">
-        <f>15720-I30+I31+I32</f>
-        <v>15007.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+    </row>
+    <row r="34" spans="1:1">
       <c r="A34" s="1"/>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:1">
       <c r="A35" s="1"/>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:1">
       <c r="A36" s="1"/>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:1">
       <c r="A37" s="1"/>
-      <c r="I37">
-        <f>+G22</f>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="I38">
-        <f>+G23</f>
-        <v>10800</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="I39">
-        <f>10864+I38-I37</f>
-        <v>-336</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G25" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="AL41"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:G25" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G17">
     <sortCondition ref="A2:A17"/>
   </sortState>
@@ -1413,7 +1576,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8AE11B3-0E9A-43BD-8421-E8F835D75104}">
-  <dimension ref="A1:Z250"/>
+  <dimension ref="A1:AA250"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.85546875" customWidth="1"/>
@@ -1422,87 +1585,90 @@
     <col min="9" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" t="s">
         <v>17</v>
       </c>
-      <c r="K1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L1" t="s">
-        <v>15</v>
-      </c>
       <c r="M1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="R1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="U1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="V1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="W1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="X1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:26">
+        <v>56</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
       <c r="A2" s="1">
         <v>45569</v>
       </c>
@@ -1598,8 +1764,11 @@
         <f t="shared" ref="X2:X12" si="22">+X3-0.1</f>
         <v>88.210000000000065</v>
       </c>
-    </row>
-    <row r="3" spans="1:26">
+      <c r="AA2">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27">
       <c r="A3" s="1">
         <v>45570</v>
       </c>
@@ -1695,8 +1864,12 @@
         <f t="shared" si="22"/>
         <v>88.310000000000059</v>
       </c>
-    </row>
-    <row r="4" spans="1:26">
+      <c r="AA3" s="7">
+        <f>+AA2+1</f>
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27">
       <c r="A4" s="1">
         <v>45571</v>
       </c>
@@ -1792,8 +1965,12 @@
         <f t="shared" si="22"/>
         <v>88.410000000000053</v>
       </c>
-    </row>
-    <row r="5" spans="1:26">
+      <c r="AA4" s="7">
+        <f t="shared" ref="AA4:AA67" si="23">+AA3+1</f>
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27">
       <c r="A5" s="1">
         <v>45572</v>
       </c>
@@ -1889,8 +2066,12 @@
         <f t="shared" si="22"/>
         <v>88.510000000000048</v>
       </c>
-    </row>
-    <row r="6" spans="1:26">
+      <c r="AA5" s="7">
+        <f t="shared" si="23"/>
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27">
       <c r="A6" s="1">
         <v>45573</v>
       </c>
@@ -1986,8 +2167,12 @@
         <f t="shared" si="22"/>
         <v>88.610000000000042</v>
       </c>
-    </row>
-    <row r="7" spans="1:26">
+      <c r="AA6" s="7">
+        <f t="shared" si="23"/>
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27">
       <c r="A7" s="1">
         <v>45574</v>
       </c>
@@ -2083,8 +2268,12 @@
         <f t="shared" si="22"/>
         <v>88.710000000000036</v>
       </c>
-    </row>
-    <row r="8" spans="1:26">
+      <c r="AA7" s="7">
+        <f t="shared" si="23"/>
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27">
       <c r="A8" s="1">
         <v>45575</v>
       </c>
@@ -2180,8 +2369,12 @@
         <f t="shared" si="22"/>
         <v>88.810000000000031</v>
       </c>
-    </row>
-    <row r="9" spans="1:26">
+      <c r="AA8" s="7">
+        <f t="shared" si="23"/>
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27">
       <c r="A9" s="1">
         <v>45576</v>
       </c>
@@ -2277,8 +2470,12 @@
         <f t="shared" si="22"/>
         <v>88.910000000000025</v>
       </c>
-    </row>
-    <row r="10" spans="1:26">
+      <c r="AA9" s="7">
+        <f t="shared" si="23"/>
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27">
       <c r="A10" s="1">
         <v>45577</v>
       </c>
@@ -2374,8 +2571,12 @@
         <f t="shared" si="22"/>
         <v>89.010000000000019</v>
       </c>
-    </row>
-    <row r="11" spans="1:26">
+      <c r="AA10" s="7">
+        <f t="shared" si="23"/>
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27">
       <c r="A11" s="1">
         <v>45578</v>
       </c>
@@ -2471,8 +2672,12 @@
         <f t="shared" si="22"/>
         <v>89.110000000000014</v>
       </c>
-    </row>
-    <row r="12" spans="1:26">
+      <c r="AA11" s="7">
+        <f t="shared" si="23"/>
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27">
       <c r="A12" s="1">
         <v>45579</v>
       </c>
@@ -2568,8 +2773,12 @@
         <f t="shared" si="22"/>
         <v>89.210000000000008</v>
       </c>
-    </row>
-    <row r="13" spans="1:26">
+      <c r="AA12" s="7">
+        <f t="shared" si="23"/>
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27">
       <c r="A13" s="1">
         <v>45580</v>
       </c>
@@ -2578,95 +2787,99 @@
         <v>72.5</v>
       </c>
       <c r="C13">
-        <f t="shared" ref="C13:X13" si="23">+C14-0.1</f>
+        <f t="shared" ref="C13:X13" si="24">+C14-0.1</f>
         <v>64.900000000000006</v>
       </c>
       <c r="D13">
+        <f t="shared" si="24"/>
+        <v>56.809999999999995</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="24"/>
+        <v>61.269999999999996</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="24"/>
+        <v>52.6</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="24"/>
+        <v>59.019999999999996</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="24"/>
+        <v>71.36</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="24"/>
+        <v>63.16</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="24"/>
+        <v>56.68</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="24"/>
+        <v>58.89</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="24"/>
+        <v>52.6</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="24"/>
+        <v>98.800000000000011</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="24"/>
+        <v>94</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="24"/>
+        <v>88.300000000000011</v>
+      </c>
+      <c r="P13">
+        <f t="shared" si="24"/>
+        <v>87.73</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="24"/>
+        <v>74.600000000000009</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="24"/>
+        <v>91.660000000000011</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="24"/>
+        <v>95.7</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="24"/>
+        <v>91.65</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="24"/>
+        <v>85.9</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="24"/>
+        <v>84.7</v>
+      </c>
+      <c r="W13">
+        <f t="shared" si="24"/>
+        <v>72.900000000000006</v>
+      </c>
+      <c r="X13">
+        <f t="shared" si="24"/>
+        <v>89.31</v>
+      </c>
+      <c r="AA13" s="7">
         <f t="shared" si="23"/>
-        <v>56.809999999999995</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="23"/>
-        <v>61.269999999999996</v>
-      </c>
-      <c r="F13">
-        <f t="shared" si="23"/>
-        <v>52.6</v>
-      </c>
-      <c r="G13">
-        <f t="shared" si="23"/>
-        <v>59.019999999999996</v>
-      </c>
-      <c r="H13">
-        <f t="shared" si="23"/>
-        <v>71.36</v>
-      </c>
-      <c r="I13">
-        <f t="shared" si="23"/>
-        <v>63.16</v>
-      </c>
-      <c r="J13">
-        <f t="shared" si="23"/>
-        <v>56.68</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="23"/>
-        <v>58.89</v>
-      </c>
-      <c r="L13">
-        <f t="shared" si="23"/>
-        <v>52.6</v>
-      </c>
-      <c r="M13">
-        <f t="shared" si="23"/>
-        <v>98.800000000000011</v>
-      </c>
-      <c r="N13">
-        <f t="shared" si="23"/>
-        <v>94</v>
-      </c>
-      <c r="O13">
-        <f t="shared" si="23"/>
-        <v>88.300000000000011</v>
-      </c>
-      <c r="P13">
-        <f t="shared" si="23"/>
-        <v>87.73</v>
-      </c>
-      <c r="Q13">
-        <f t="shared" si="23"/>
-        <v>74.600000000000009</v>
-      </c>
-      <c r="R13">
-        <f t="shared" si="23"/>
-        <v>91.660000000000011</v>
-      </c>
-      <c r="S13">
-        <f t="shared" si="23"/>
-        <v>95.7</v>
-      </c>
-      <c r="T13">
-        <f t="shared" si="23"/>
-        <v>91.65</v>
-      </c>
-      <c r="U13">
-        <f t="shared" si="23"/>
-        <v>85.9</v>
-      </c>
-      <c r="V13">
-        <f t="shared" si="23"/>
-        <v>84.7</v>
-      </c>
-      <c r="W13">
-        <f t="shared" si="23"/>
-        <v>72.900000000000006</v>
-      </c>
-      <c r="X13">
-        <f t="shared" si="23"/>
-        <v>89.31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27">
       <c r="A14" s="1">
         <v>45581</v>
       </c>
@@ -2739,8 +2952,12 @@
       <c r="X14">
         <v>89.41</v>
       </c>
-    </row>
-    <row r="15" spans="1:26">
+      <c r="AA14" s="7">
+        <f t="shared" si="23"/>
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27">
       <c r="A15" s="1">
         <v>45582</v>
       </c>
@@ -2813,8 +3030,12 @@
       <c r="X15">
         <v>88.5</v>
       </c>
-    </row>
-    <row r="16" spans="1:26">
+      <c r="AA15" s="7">
+        <f t="shared" si="23"/>
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27">
       <c r="A16" s="1">
         <v>45583</v>
       </c>
@@ -2887,8 +3108,12 @@
       <c r="X16">
         <v>88.3</v>
       </c>
-    </row>
-    <row r="17" spans="1:24">
+      <c r="AA16" s="7">
+        <f t="shared" si="23"/>
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27">
       <c r="A17" s="1">
         <v>45586</v>
       </c>
@@ -2961,8 +3186,12 @@
       <c r="X17">
         <v>88.62</v>
       </c>
-    </row>
-    <row r="18" spans="1:24">
+      <c r="AA17" s="7">
+        <f t="shared" si="23"/>
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27">
       <c r="A18" s="1">
         <v>45587</v>
       </c>
@@ -3035,8 +3264,12 @@
       <c r="X18">
         <v>88.35</v>
       </c>
-    </row>
-    <row r="19" spans="1:24">
+      <c r="AA18" s="7">
+        <f t="shared" si="23"/>
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27">
       <c r="A19" s="1">
         <v>45588</v>
       </c>
@@ -3109,8 +3342,12 @@
       <c r="X19">
         <v>88.25</v>
       </c>
-    </row>
-    <row r="20" spans="1:24">
+      <c r="AA19" s="7">
+        <f t="shared" si="23"/>
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27">
       <c r="A20" s="1">
         <v>45589</v>
       </c>
@@ -3183,8 +3420,12 @@
       <c r="X20">
         <v>89.2</v>
       </c>
-    </row>
-    <row r="21" spans="1:24">
+      <c r="AA20" s="7">
+        <f t="shared" si="23"/>
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27">
       <c r="A21" s="1">
         <v>45590</v>
       </c>
@@ -3257,8 +3498,12 @@
       <c r="X21">
         <v>89.2</v>
       </c>
-    </row>
-    <row r="22" spans="1:24">
+      <c r="AA21" s="7">
+        <f t="shared" si="23"/>
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27">
       <c r="A22" s="1">
         <v>45593</v>
       </c>
@@ -3331,8 +3576,12 @@
       <c r="X22">
         <v>90.06</v>
       </c>
-    </row>
-    <row r="23" spans="1:24">
+      <c r="AA22" s="7">
+        <f t="shared" si="23"/>
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27">
       <c r="A23" s="1">
         <v>45594</v>
       </c>
@@ -3405,8 +3654,12 @@
       <c r="X23">
         <v>89.35</v>
       </c>
-    </row>
-    <row r="24" spans="1:24">
+      <c r="AA23" s="7">
+        <f t="shared" si="23"/>
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27">
       <c r="A24" s="1">
         <v>45595</v>
       </c>
@@ -3479,8 +3732,12 @@
       <c r="X24">
         <v>89.75</v>
       </c>
-    </row>
-    <row r="25" spans="1:24">
+      <c r="AA24" s="7">
+        <f t="shared" si="23"/>
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27">
       <c r="A25" s="1">
         <v>45596</v>
       </c>
@@ -3553,8 +3810,12 @@
       <c r="X25">
         <v>89.5</v>
       </c>
-    </row>
-    <row r="26" spans="1:24">
+      <c r="AA25" s="7">
+        <f t="shared" si="23"/>
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27">
       <c r="A26" s="1">
         <v>45597</v>
       </c>
@@ -3627,8 +3888,12 @@
       <c r="X26">
         <v>89.5</v>
       </c>
-    </row>
-    <row r="27" spans="1:24">
+      <c r="AA26" s="7">
+        <f t="shared" si="23"/>
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27">
       <c r="A27" s="1">
         <v>45600</v>
       </c>
@@ -3701,8 +3966,12 @@
       <c r="X27">
         <v>90.2</v>
       </c>
-    </row>
-    <row r="28" spans="1:24">
+      <c r="AA27" s="7">
+        <f t="shared" si="23"/>
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27">
       <c r="A28" s="1">
         <v>45601</v>
       </c>
@@ -3775,8 +4044,12 @@
       <c r="X28">
         <v>90.2</v>
       </c>
-    </row>
-    <row r="29" spans="1:24">
+      <c r="AA28" s="7">
+        <f t="shared" si="23"/>
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27">
       <c r="A29" s="1">
         <v>45603</v>
       </c>
@@ -3849,8 +4122,12 @@
       <c r="X29">
         <v>90.4</v>
       </c>
-    </row>
-    <row r="30" spans="1:24">
+      <c r="AA29" s="7">
+        <f t="shared" si="23"/>
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27">
       <c r="A30" s="1">
         <v>45604</v>
       </c>
@@ -3923,8 +4200,12 @@
       <c r="X30">
         <v>90.5</v>
       </c>
-    </row>
-    <row r="31" spans="1:24">
+      <c r="AA30" s="7">
+        <f t="shared" si="23"/>
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27">
       <c r="A31" s="1">
         <v>45607</v>
       </c>
@@ -3997,8 +4278,12 @@
       <c r="X31">
         <v>90.85</v>
       </c>
-    </row>
-    <row r="32" spans="1:24">
+      <c r="AA31" s="7">
+        <f t="shared" si="23"/>
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27">
       <c r="A32" s="1">
         <v>45608</v>
       </c>
@@ -4071,8 +4356,12 @@
       <c r="X32">
         <v>92</v>
       </c>
-    </row>
-    <row r="33" spans="1:24">
+      <c r="AA32" s="7">
+        <f t="shared" si="23"/>
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27">
       <c r="A33" s="1">
         <v>45609</v>
       </c>
@@ -4145,8 +4434,12 @@
       <c r="X33">
         <v>92.2</v>
       </c>
-    </row>
-    <row r="34" spans="1:24">
+      <c r="AA33" s="7">
+        <f t="shared" si="23"/>
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27">
       <c r="A34" s="1">
         <v>45610</v>
       </c>
@@ -4219,8 +4512,12 @@
       <c r="X34">
         <v>91.8</v>
       </c>
-    </row>
-    <row r="35" spans="1:24">
+      <c r="AA34" s="7">
+        <f t="shared" si="23"/>
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27">
       <c r="A35" s="1">
         <v>45611</v>
       </c>
@@ -4293,8 +4590,12 @@
       <c r="X35">
         <v>91.7</v>
       </c>
-    </row>
-    <row r="36" spans="1:24">
+      <c r="AA35" s="7">
+        <f t="shared" si="23"/>
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27">
       <c r="A36" s="1">
         <v>45615</v>
       </c>
@@ -4367,8 +4668,12 @@
       <c r="X36">
         <v>91.77</v>
       </c>
-    </row>
-    <row r="37" spans="1:24">
+      <c r="AA36" s="7">
+        <f t="shared" si="23"/>
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27">
       <c r="A37" s="1">
         <v>45616</v>
       </c>
@@ -4441,8 +4746,12 @@
       <c r="X37">
         <v>91.85</v>
       </c>
-    </row>
-    <row r="38" spans="1:24">
+      <c r="AA37" s="7">
+        <f t="shared" si="23"/>
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27">
       <c r="A38" s="1">
         <v>45617</v>
       </c>
@@ -4515,8 +4824,12 @@
       <c r="X38">
         <v>91.6</v>
       </c>
-    </row>
-    <row r="39" spans="1:24">
+      <c r="AA38" s="7">
+        <f t="shared" si="23"/>
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27">
       <c r="A39" s="1">
         <v>45618</v>
       </c>
@@ -4589,8 +4902,12 @@
       <c r="X39">
         <v>91.5</v>
       </c>
-    </row>
-    <row r="40" spans="1:24">
+      <c r="AA39" s="7">
+        <f t="shared" si="23"/>
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27">
       <c r="A40" s="1">
         <v>45621</v>
       </c>
@@ -4663,8 +4980,12 @@
       <c r="X40">
         <v>91.65</v>
       </c>
-    </row>
-    <row r="41" spans="1:24">
+      <c r="AA40" s="7">
+        <f t="shared" si="23"/>
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27">
       <c r="A41" s="1">
         <v>45622</v>
       </c>
@@ -4737,8 +5058,12 @@
       <c r="X41">
         <v>91.5</v>
       </c>
-    </row>
-    <row r="42" spans="1:24">
+      <c r="AA41" s="7">
+        <f t="shared" si="23"/>
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27">
       <c r="A42" s="1">
         <v>45623</v>
       </c>
@@ -4811,8 +5136,12 @@
       <c r="X42">
         <v>91.5</v>
       </c>
-    </row>
-    <row r="43" spans="1:24">
+      <c r="AA42" s="7">
+        <f t="shared" si="23"/>
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27">
       <c r="A43" s="1">
         <v>45624</v>
       </c>
@@ -4885,8 +5214,12 @@
       <c r="X43">
         <v>91.5</v>
       </c>
-    </row>
-    <row r="44" spans="1:24">
+      <c r="AA43" s="7">
+        <f t="shared" si="23"/>
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27">
       <c r="A44" s="1">
         <v>45625</v>
       </c>
@@ -4959,8 +5292,12 @@
       <c r="X44">
         <v>91.55</v>
       </c>
-    </row>
-    <row r="45" spans="1:24">
+      <c r="AA44" s="7">
+        <f t="shared" si="23"/>
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27">
       <c r="A45" s="1">
         <v>45628</v>
       </c>
@@ -5033,8 +5370,12 @@
       <c r="X45">
         <v>92</v>
       </c>
-    </row>
-    <row r="46" spans="1:24">
+      <c r="AA45" s="7">
+        <f t="shared" si="23"/>
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27">
       <c r="A46" s="1">
         <v>45629</v>
       </c>
@@ -5107,8 +5448,12 @@
       <c r="X46">
         <v>91.5</v>
       </c>
-    </row>
-    <row r="47" spans="1:24">
+      <c r="AA46" s="7">
+        <f t="shared" si="23"/>
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="47" spans="1:27">
       <c r="A47" s="1">
         <v>45630</v>
       </c>
@@ -5181,8 +5526,12 @@
       <c r="X47">
         <v>91.25</v>
       </c>
-    </row>
-    <row r="48" spans="1:24">
+      <c r="AA47" s="7">
+        <f t="shared" si="23"/>
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="48" spans="1:27">
       <c r="A48" s="1">
         <v>45631</v>
       </c>
@@ -5255,8 +5604,12 @@
       <c r="X48">
         <v>91.5</v>
       </c>
-    </row>
-    <row r="49" spans="1:24">
+      <c r="AA48" s="7">
+        <f t="shared" si="23"/>
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27">
       <c r="A49" s="1">
         <v>45632</v>
       </c>
@@ -5329,8 +5682,12 @@
       <c r="X49">
         <v>92.35</v>
       </c>
-    </row>
-    <row r="50" spans="1:24">
+      <c r="AA49" s="7">
+        <f t="shared" si="23"/>
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27">
       <c r="A50" s="1">
         <v>45635</v>
       </c>
@@ -5403,8 +5760,12 @@
       <c r="X50">
         <v>91.81</v>
       </c>
-    </row>
-    <row r="51" spans="1:24">
+      <c r="AA50" s="7">
+        <f t="shared" si="23"/>
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27">
       <c r="A51" s="1">
         <v>45636</v>
       </c>
@@ -5477,8 +5838,12 @@
       <c r="X51">
         <v>91.5</v>
       </c>
-    </row>
-    <row r="52" spans="1:24">
+      <c r="AA51" s="7">
+        <f t="shared" si="23"/>
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27">
       <c r="A52" s="1">
         <v>45637</v>
       </c>
@@ -5551,8 +5916,12 @@
       <c r="X52">
         <v>91.5</v>
       </c>
-    </row>
-    <row r="53" spans="1:24">
+      <c r="AA52" s="7">
+        <f t="shared" si="23"/>
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27">
       <c r="A53" s="1">
         <v>45638</v>
       </c>
@@ -5625,8 +5994,12 @@
       <c r="X53">
         <v>91.65</v>
       </c>
-    </row>
-    <row r="54" spans="1:24">
+      <c r="AA53" s="7">
+        <f t="shared" si="23"/>
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27">
       <c r="A54" s="1">
         <v>45639</v>
       </c>
@@ -5699,8 +6072,12 @@
       <c r="X54">
         <v>91.4</v>
       </c>
-    </row>
-    <row r="55" spans="1:24">
+      <c r="AA54" s="7">
+        <f t="shared" si="23"/>
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27">
       <c r="A55" s="1">
         <v>45642</v>
       </c>
@@ -5773,8 +6150,12 @@
       <c r="X55">
         <v>91.35</v>
       </c>
-    </row>
-    <row r="56" spans="1:24">
+      <c r="AA55" s="7">
+        <f t="shared" si="23"/>
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27">
       <c r="A56" s="1">
         <v>45643</v>
       </c>
@@ -5847,8 +6228,12 @@
       <c r="X56">
         <v>90.95</v>
       </c>
-    </row>
-    <row r="57" spans="1:24">
+      <c r="AA56" s="7">
+        <f t="shared" si="23"/>
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="57" spans="1:27">
       <c r="A57" s="1">
         <v>45644</v>
       </c>
@@ -5921,8 +6306,12 @@
       <c r="X57">
         <v>91.2</v>
       </c>
-    </row>
-    <row r="58" spans="1:24">
+      <c r="AA57" s="7">
+        <f t="shared" si="23"/>
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="58" spans="1:27">
       <c r="A58" s="1">
         <v>45645</v>
       </c>
@@ -5995,8 +6384,12 @@
       <c r="X58">
         <v>91</v>
       </c>
-    </row>
-    <row r="59" spans="1:24">
+      <c r="AA58" s="7">
+        <f t="shared" si="23"/>
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="59" spans="1:27">
       <c r="A59" s="1">
         <v>45646</v>
       </c>
@@ -6069,8 +6462,12 @@
       <c r="X59">
         <v>90.8</v>
       </c>
-    </row>
-    <row r="60" spans="1:24">
+      <c r="AA59" s="7">
+        <f t="shared" si="23"/>
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="60" spans="1:27">
       <c r="A60" s="1">
         <v>45649</v>
       </c>
@@ -6143,8 +6540,12 @@
       <c r="X60">
         <v>91.7</v>
       </c>
-    </row>
-    <row r="61" spans="1:24">
+      <c r="AA60" s="7">
+        <f t="shared" si="23"/>
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="61" spans="1:27">
       <c r="A61" s="1">
         <v>45652</v>
       </c>
@@ -6217,8 +6618,12 @@
       <c r="X61">
         <v>92.1</v>
       </c>
-    </row>
-    <row r="62" spans="1:24">
+      <c r="AA61" s="7">
+        <f t="shared" si="23"/>
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="62" spans="1:27">
       <c r="A62" s="1">
         <v>45653</v>
       </c>
@@ -6291,8 +6696,12 @@
       <c r="X62">
         <v>92.5</v>
       </c>
-    </row>
-    <row r="63" spans="1:24">
+      <c r="AA62" s="7">
+        <f t="shared" si="23"/>
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="63" spans="1:27">
       <c r="A63" s="1">
         <v>45656</v>
       </c>
@@ -6365,8 +6774,12 @@
       <c r="X63">
         <v>93.5</v>
       </c>
-    </row>
-    <row r="64" spans="1:24">
+      <c r="AA63" s="7">
+        <f t="shared" si="23"/>
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="64" spans="1:27">
       <c r="A64" s="1">
         <v>45659</v>
       </c>
@@ -6439,8 +6852,12 @@
       <c r="X64">
         <v>93.16</v>
       </c>
-    </row>
-    <row r="65" spans="1:24">
+      <c r="AA64" s="7">
+        <f t="shared" si="23"/>
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="65" spans="1:27">
       <c r="A65" s="1">
         <v>45660</v>
       </c>
@@ -6513,8 +6930,12 @@
       <c r="X65">
         <v>93.9</v>
       </c>
-    </row>
-    <row r="66" spans="1:24">
+      <c r="AA65" s="7">
+        <f t="shared" si="23"/>
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="66" spans="1:27">
       <c r="A66" s="1">
         <v>45663</v>
       </c>
@@ -6587,8 +7008,12 @@
       <c r="X66">
         <v>93.95</v>
       </c>
-    </row>
-    <row r="67" spans="1:24">
+      <c r="AA66" s="7">
+        <f t="shared" si="23"/>
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="67" spans="1:27">
       <c r="A67" s="1">
         <v>45664</v>
       </c>
@@ -6661,8 +7086,12 @@
       <c r="X67">
         <v>94.2</v>
       </c>
-    </row>
-    <row r="68" spans="1:24">
+      <c r="AA67" s="7">
+        <f t="shared" si="23"/>
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="68" spans="1:27">
       <c r="A68" s="1">
         <v>45665</v>
       </c>
@@ -6735,8 +7164,12 @@
       <c r="X68">
         <v>93.9</v>
       </c>
-    </row>
-    <row r="69" spans="1:24">
+      <c r="AA68" s="7">
+        <f t="shared" ref="AA68:AA131" si="25">+AA67+1</f>
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="69" spans="1:27">
       <c r="A69" s="1">
         <v>45666</v>
       </c>
@@ -6809,8 +7242,12 @@
       <c r="X69">
         <v>93.8</v>
       </c>
-    </row>
-    <row r="70" spans="1:24">
+      <c r="AA69" s="7">
+        <f t="shared" si="25"/>
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="70" spans="1:27">
       <c r="A70" s="1">
         <v>45667</v>
       </c>
@@ -6883,8 +7320,12 @@
       <c r="X70">
         <v>94.15</v>
       </c>
-    </row>
-    <row r="71" spans="1:24">
+      <c r="AA70" s="7">
+        <f t="shared" si="25"/>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="71" spans="1:27">
       <c r="A71" s="1">
         <v>45670</v>
       </c>
@@ -6957,8 +7398,12 @@
       <c r="X71">
         <v>94</v>
       </c>
-    </row>
-    <row r="72" spans="1:24">
+      <c r="AA71" s="7">
+        <f t="shared" si="25"/>
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="72" spans="1:27">
       <c r="A72" s="1">
         <v>45671</v>
       </c>
@@ -7031,8 +7476,12 @@
       <c r="X72">
         <v>94.15</v>
       </c>
-    </row>
-    <row r="73" spans="1:24">
+      <c r="AA72" s="7">
+        <f t="shared" si="25"/>
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="73" spans="1:27">
       <c r="A73" s="1">
         <v>45672</v>
       </c>
@@ -7105,8 +7554,12 @@
       <c r="X73">
         <v>94.15</v>
       </c>
-    </row>
-    <row r="74" spans="1:24">
+      <c r="AA73" s="7">
+        <f t="shared" si="25"/>
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="74" spans="1:27">
       <c r="A74" s="1">
         <v>45673</v>
       </c>
@@ -7179,8 +7632,12 @@
       <c r="X74">
         <v>93.85</v>
       </c>
-    </row>
-    <row r="75" spans="1:24">
+      <c r="AA74" s="7">
+        <f t="shared" si="25"/>
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="75" spans="1:27">
       <c r="A75" s="1">
         <v>45674</v>
       </c>
@@ -7253,8 +7710,12 @@
       <c r="X75">
         <v>94</v>
       </c>
-    </row>
-    <row r="76" spans="1:24">
+      <c r="AA75" s="7">
+        <f t="shared" si="25"/>
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="76" spans="1:27">
       <c r="A76" s="1">
         <v>45677</v>
       </c>
@@ -7327,8 +7788,12 @@
       <c r="X76">
         <v>94.15</v>
       </c>
-    </row>
-    <row r="77" spans="1:24">
+      <c r="AA76" s="7">
+        <f t="shared" si="25"/>
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="77" spans="1:27">
       <c r="A77" s="1">
         <v>45678</v>
       </c>
@@ -7401,8 +7866,12 @@
       <c r="X77">
         <v>94</v>
       </c>
-    </row>
-    <row r="78" spans="1:24">
+      <c r="AA77" s="7">
+        <f t="shared" si="25"/>
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="78" spans="1:27">
       <c r="A78" s="1">
         <v>45679</v>
       </c>
@@ -7475,8 +7944,12 @@
       <c r="X78">
         <v>94.15</v>
       </c>
-    </row>
-    <row r="79" spans="1:24">
+      <c r="AA78" s="7">
+        <f t="shared" si="25"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="79" spans="1:27">
       <c r="A79" s="1">
         <v>45680</v>
       </c>
@@ -7549,8 +8022,12 @@
       <c r="X79">
         <v>94.23</v>
       </c>
-    </row>
-    <row r="80" spans="1:24">
+      <c r="AA79" s="7">
+        <f t="shared" si="25"/>
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="80" spans="1:27">
       <c r="A80" s="1">
         <v>45681</v>
       </c>
@@ -7623,8 +8100,12 @@
       <c r="X80">
         <v>94.75</v>
       </c>
-    </row>
-    <row r="81" spans="1:24">
+      <c r="AA80" s="7">
+        <f t="shared" si="25"/>
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="81" spans="1:27">
       <c r="A81" s="1">
         <v>45684</v>
       </c>
@@ -7697,8 +8178,12 @@
       <c r="X81">
         <v>95</v>
       </c>
-    </row>
-    <row r="82" spans="1:24">
+      <c r="AA81" s="7">
+        <f t="shared" si="25"/>
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="82" spans="1:27">
       <c r="A82" s="1">
         <v>45685</v>
       </c>
@@ -7771,8 +8256,12 @@
       <c r="X82">
         <v>95.45</v>
       </c>
-    </row>
-    <row r="83" spans="1:24">
+      <c r="AA82" s="7">
+        <f t="shared" si="25"/>
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="83" spans="1:27">
       <c r="A83" s="1">
         <v>45686</v>
       </c>
@@ -7845,8 +8334,12 @@
       <c r="X83">
         <v>95.26</v>
       </c>
-    </row>
-    <row r="84" spans="1:24">
+      <c r="AA83" s="7">
+        <f t="shared" si="25"/>
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="84" spans="1:27">
       <c r="A84" s="1">
         <v>45687</v>
       </c>
@@ -7919,8 +8412,12 @@
       <c r="X84">
         <v>95.4</v>
       </c>
-    </row>
-    <row r="85" spans="1:24">
+      <c r="AA84" s="7">
+        <f t="shared" si="25"/>
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="85" spans="1:27">
       <c r="A85" s="1">
         <v>45688</v>
       </c>
@@ -7993,8 +8490,12 @@
       <c r="X85">
         <v>95.19</v>
       </c>
-    </row>
-    <row r="86" spans="1:24">
+      <c r="AA85" s="7">
+        <f t="shared" si="25"/>
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="86" spans="1:27">
       <c r="A86" s="1">
         <v>45691</v>
       </c>
@@ -8067,8 +8568,12 @@
       <c r="X86">
         <v>95.22</v>
       </c>
-    </row>
-    <row r="87" spans="1:24">
+      <c r="AA86" s="7">
+        <f t="shared" si="25"/>
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="87" spans="1:27">
       <c r="A87" s="1">
         <v>45692</v>
       </c>
@@ -8141,8 +8646,12 @@
       <c r="X87">
         <v>95.25</v>
       </c>
-    </row>
-    <row r="88" spans="1:24">
+      <c r="AA87" s="7">
+        <f t="shared" si="25"/>
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="88" spans="1:27">
       <c r="A88" s="1">
         <v>45693</v>
       </c>
@@ -8215,8 +8724,12 @@
       <c r="X88">
         <v>95.3</v>
       </c>
-    </row>
-    <row r="89" spans="1:24">
+      <c r="AA88" s="7">
+        <f t="shared" si="25"/>
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="89" spans="1:27">
       <c r="A89" s="1">
         <v>45694</v>
       </c>
@@ -8289,8 +8802,12 @@
       <c r="X89">
         <v>95.25</v>
       </c>
-    </row>
-    <row r="90" spans="1:24">
+      <c r="AA89" s="7">
+        <f t="shared" si="25"/>
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="90" spans="1:27">
       <c r="A90" s="1">
         <v>45695</v>
       </c>
@@ -8363,8 +8880,12 @@
       <c r="X90">
         <v>95.7</v>
       </c>
-    </row>
-    <row r="91" spans="1:24">
+      <c r="AA90" s="7">
+        <f t="shared" si="25"/>
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="91" spans="1:27">
       <c r="A91" s="1">
         <v>45698</v>
       </c>
@@ -8437,8 +8958,12 @@
       <c r="X91">
         <v>95.7</v>
       </c>
-    </row>
-    <row r="92" spans="1:24">
+      <c r="AA91" s="7">
+        <f t="shared" si="25"/>
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="92" spans="1:27">
       <c r="A92" s="1">
         <v>45699</v>
       </c>
@@ -8511,8 +9036,12 @@
       <c r="X92">
         <v>95.4</v>
       </c>
-    </row>
-    <row r="93" spans="1:24">
+      <c r="AA92" s="7">
+        <f t="shared" si="25"/>
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="93" spans="1:27">
       <c r="A93" s="1">
         <v>45700</v>
       </c>
@@ -8585,8 +9114,12 @@
       <c r="X93">
         <v>95.2</v>
       </c>
-    </row>
-    <row r="94" spans="1:24">
+      <c r="AA93" s="7">
+        <f t="shared" si="25"/>
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="94" spans="1:27">
       <c r="A94" s="1">
         <v>45701</v>
       </c>
@@ -8659,8 +9192,12 @@
       <c r="X94">
         <v>95.5</v>
       </c>
-    </row>
-    <row r="95" spans="1:24">
+      <c r="AA94" s="7">
+        <f t="shared" si="25"/>
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="95" spans="1:27">
       <c r="A95" s="1">
         <v>45702</v>
       </c>
@@ -8733,8 +9270,12 @@
       <c r="X95">
         <v>95.25</v>
       </c>
-    </row>
-    <row r="96" spans="1:24">
+      <c r="AA95" s="7">
+        <f t="shared" si="25"/>
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="96" spans="1:27">
       <c r="A96" s="1">
         <v>45705</v>
       </c>
@@ -8807,8 +9348,12 @@
       <c r="X96">
         <v>94.8</v>
       </c>
-    </row>
-    <row r="97" spans="1:24">
+      <c r="AA96" s="7">
+        <f t="shared" si="25"/>
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="97" spans="1:27">
       <c r="A97" s="1">
         <v>45706</v>
       </c>
@@ -8881,8 +9426,12 @@
       <c r="X97">
         <v>94.98</v>
       </c>
-    </row>
-    <row r="98" spans="1:24">
+      <c r="AA97" s="7">
+        <f t="shared" si="25"/>
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="98" spans="1:27">
       <c r="A98" s="1">
         <v>45707</v>
       </c>
@@ -8955,8 +9504,12 @@
       <c r="X98">
         <v>94.8</v>
       </c>
-    </row>
-    <row r="99" spans="1:24">
+      <c r="AA98" s="7">
+        <f t="shared" si="25"/>
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="99" spans="1:27">
       <c r="A99" s="1">
         <v>45708</v>
       </c>
@@ -9029,8 +9582,12 @@
       <c r="X99">
         <v>95.32</v>
       </c>
-    </row>
-    <row r="100" spans="1:24">
+      <c r="AA99" s="7">
+        <f t="shared" si="25"/>
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="100" spans="1:27">
       <c r="A100" s="1">
         <v>45709</v>
       </c>
@@ -9103,8 +9660,12 @@
       <c r="X100">
         <v>95.2</v>
       </c>
-    </row>
-    <row r="101" spans="1:24">
+      <c r="AA100" s="7">
+        <f t="shared" si="25"/>
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="101" spans="1:27">
       <c r="A101" s="1">
         <v>45712</v>
       </c>
@@ -9177,8 +9738,12 @@
       <c r="X101">
         <v>95</v>
       </c>
-    </row>
-    <row r="102" spans="1:24">
+      <c r="AA101" s="7">
+        <f t="shared" si="25"/>
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="102" spans="1:27">
       <c r="A102" s="1">
         <v>45713</v>
       </c>
@@ -9251,8 +9816,12 @@
       <c r="X102">
         <v>95.1</v>
       </c>
-    </row>
-    <row r="103" spans="1:24">
+      <c r="AA102" s="7">
+        <f t="shared" si="25"/>
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="103" spans="1:27">
       <c r="A103" s="1">
         <v>45714</v>
       </c>
@@ -9325,8 +9894,12 @@
       <c r="X103">
         <v>95.1</v>
       </c>
-    </row>
-    <row r="104" spans="1:24">
+      <c r="AA103" s="7">
+        <f t="shared" si="25"/>
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="104" spans="1:27">
       <c r="A104" s="1">
         <v>45715</v>
       </c>
@@ -9399,8 +9972,12 @@
       <c r="X104">
         <v>94.44</v>
       </c>
-    </row>
-    <row r="105" spans="1:24">
+      <c r="AA104" s="7">
+        <f t="shared" si="25"/>
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="105" spans="1:27">
       <c r="A105" s="1">
         <v>45716</v>
       </c>
@@ -9473,8 +10050,12 @@
       <c r="X105">
         <v>94</v>
       </c>
-    </row>
-    <row r="106" spans="1:24">
+      <c r="AA105" s="7">
+        <f t="shared" si="25"/>
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="106" spans="1:27">
       <c r="A106" s="1">
         <v>45721</v>
       </c>
@@ -9547,8 +10128,12 @@
       <c r="X106">
         <v>94.5</v>
       </c>
-    </row>
-    <row r="107" spans="1:24">
+      <c r="AA106" s="7">
+        <f t="shared" si="25"/>
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="107" spans="1:27">
       <c r="A107" s="1">
         <v>45722</v>
       </c>
@@ -9621,8 +10206,12 @@
       <c r="X107">
         <v>94.65</v>
       </c>
-    </row>
-    <row r="108" spans="1:24">
+      <c r="AA107" s="7">
+        <f t="shared" si="25"/>
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="108" spans="1:27">
       <c r="A108" s="1">
         <v>45723</v>
       </c>
@@ -9695,8 +10284,12 @@
       <c r="X108">
         <v>95.04</v>
       </c>
-    </row>
-    <row r="109" spans="1:24">
+      <c r="AA108" s="7">
+        <f t="shared" si="25"/>
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="109" spans="1:27">
       <c r="A109" s="1">
         <v>45726</v>
       </c>
@@ -9769,8 +10362,12 @@
       <c r="X109">
         <v>94.85</v>
       </c>
-    </row>
-    <row r="110" spans="1:24">
+      <c r="AA109" s="7">
+        <f t="shared" si="25"/>
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="110" spans="1:27">
       <c r="A110" s="1">
         <v>45727</v>
       </c>
@@ -9843,8 +10440,12 @@
       <c r="X110">
         <v>95.05</v>
       </c>
-    </row>
-    <row r="111" spans="1:24">
+      <c r="AA110" s="7">
+        <f t="shared" si="25"/>
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="111" spans="1:27">
       <c r="A111" s="1">
         <v>45728</v>
       </c>
@@ -9917,8 +10518,12 @@
       <c r="X111">
         <v>94.5</v>
       </c>
-    </row>
-    <row r="112" spans="1:24">
+      <c r="AA111" s="7">
+        <f t="shared" si="25"/>
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="112" spans="1:27">
       <c r="A112" s="1">
         <v>45729</v>
       </c>
@@ -9991,8 +10596,12 @@
       <c r="X112">
         <v>94.43</v>
       </c>
-    </row>
-    <row r="113" spans="1:24">
+      <c r="AA112" s="7">
+        <f t="shared" si="25"/>
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="113" spans="1:27">
       <c r="A113" s="1">
         <v>45730</v>
       </c>
@@ -10065,8 +10674,12 @@
       <c r="X113">
         <v>94.6</v>
       </c>
-    </row>
-    <row r="114" spans="1:24">
+      <c r="AA113" s="7">
+        <f t="shared" si="25"/>
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="114" spans="1:27">
       <c r="A114" s="1">
         <v>45733</v>
       </c>
@@ -10139,8 +10752,12 @@
       <c r="X114">
         <v>94.1</v>
       </c>
-    </row>
-    <row r="115" spans="1:24">
+      <c r="AA114" s="7">
+        <f t="shared" si="25"/>
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="115" spans="1:27">
       <c r="A115" s="1">
         <v>45734</v>
       </c>
@@ -10213,8 +10830,12 @@
       <c r="X115">
         <v>94.49</v>
       </c>
-    </row>
-    <row r="116" spans="1:24">
+      <c r="AA115" s="7">
+        <f t="shared" si="25"/>
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="116" spans="1:27">
       <c r="A116" s="1">
         <v>45735</v>
       </c>
@@ -10287,8 +10908,12 @@
       <c r="X116">
         <v>94.17</v>
       </c>
-    </row>
-    <row r="117" spans="1:24">
+      <c r="AA116" s="7">
+        <f t="shared" si="25"/>
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="117" spans="1:27">
       <c r="A117" s="1">
         <v>45736</v>
       </c>
@@ -10361,8 +10986,12 @@
       <c r="X117">
         <v>94.35</v>
       </c>
-    </row>
-    <row r="118" spans="1:24">
+      <c r="AA117" s="7">
+        <f t="shared" si="25"/>
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="118" spans="1:27">
       <c r="A118" s="1">
         <v>45737</v>
       </c>
@@ -10435,8 +11064,12 @@
       <c r="X118">
         <v>95.2</v>
       </c>
-    </row>
-    <row r="119" spans="1:24">
+      <c r="AA118" s="7">
+        <f t="shared" si="25"/>
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="119" spans="1:27">
       <c r="A119" s="1">
         <v>45741</v>
       </c>
@@ -10509,8 +11142,12 @@
       <c r="X119">
         <v>96</v>
       </c>
-    </row>
-    <row r="120" spans="1:24">
+      <c r="AA119" s="7">
+        <f t="shared" si="25"/>
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="120" spans="1:27">
       <c r="A120" s="1">
         <v>45742</v>
       </c>
@@ -10583,8 +11220,12 @@
       <c r="X120">
         <v>96.65</v>
       </c>
-    </row>
-    <row r="121" spans="1:24">
+      <c r="AA120" s="7">
+        <f t="shared" si="25"/>
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="121" spans="1:27">
       <c r="A121" s="1">
         <v>45743</v>
       </c>
@@ -10657,8 +11298,12 @@
       <c r="X121">
         <v>96.8</v>
       </c>
-    </row>
-    <row r="122" spans="1:24">
+      <c r="AA121" s="7">
+        <f t="shared" si="25"/>
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="122" spans="1:27">
       <c r="A122" s="1">
         <v>45744</v>
       </c>
@@ -10731,8 +11376,12 @@
       <c r="X122">
         <v>96.27</v>
       </c>
-    </row>
-    <row r="123" spans="1:24">
+      <c r="AA122" s="7">
+        <f t="shared" si="25"/>
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="123" spans="1:27">
       <c r="A123" s="1">
         <v>45747</v>
       </c>
@@ -10805,8 +11454,12 @@
       <c r="X123">
         <v>96.72</v>
       </c>
-    </row>
-    <row r="124" spans="1:24">
+      <c r="AA123" s="7">
+        <f t="shared" si="25"/>
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="124" spans="1:27">
       <c r="A124" s="1">
         <v>45748</v>
       </c>
@@ -10879,8 +11532,12 @@
       <c r="X124">
         <v>97</v>
       </c>
-    </row>
-    <row r="125" spans="1:24">
+      <c r="AA124" s="7">
+        <f t="shared" si="25"/>
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="125" spans="1:27">
       <c r="A125" s="1">
         <v>45750</v>
       </c>
@@ -10953,8 +11610,12 @@
       <c r="X125">
         <v>96.65</v>
       </c>
-    </row>
-    <row r="126" spans="1:24">
+      <c r="AA125" s="7">
+        <f t="shared" si="25"/>
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="126" spans="1:27">
       <c r="A126" s="1">
         <v>45751</v>
       </c>
@@ -11027,8 +11688,12 @@
       <c r="X126">
         <v>95.96</v>
       </c>
-    </row>
-    <row r="127" spans="1:24">
+      <c r="AA126" s="7">
+        <f t="shared" si="25"/>
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="127" spans="1:27">
       <c r="A127" s="1">
         <v>45754</v>
       </c>
@@ -11101,8 +11766,12 @@
       <c r="X127">
         <v>95.25</v>
       </c>
-    </row>
-    <row r="128" spans="1:24">
+      <c r="AA127" s="7">
+        <f t="shared" si="25"/>
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="128" spans="1:27">
       <c r="A128" s="1">
         <v>45755</v>
       </c>
@@ -11175,8 +11844,12 @@
       <c r="X128">
         <v>95.5</v>
       </c>
-    </row>
-    <row r="129" spans="1:24">
+      <c r="AA128" s="7">
+        <f t="shared" si="25"/>
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="129" spans="1:27">
       <c r="A129" s="1">
         <v>45756</v>
       </c>
@@ -11249,8 +11922,12 @@
       <c r="X129">
         <v>96.9</v>
       </c>
-    </row>
-    <row r="130" spans="1:24">
+      <c r="AA129" s="7">
+        <f t="shared" si="25"/>
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="130" spans="1:27">
       <c r="A130" s="1">
         <v>45757</v>
       </c>
@@ -11323,8 +12000,12 @@
       <c r="X130">
         <v>97.54</v>
       </c>
-    </row>
-    <row r="131" spans="1:24">
+      <c r="AA130" s="7">
+        <f t="shared" si="25"/>
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="131" spans="1:27">
       <c r="A131" s="1">
         <v>45758</v>
       </c>
@@ -11397,8 +12078,12 @@
       <c r="X131">
         <v>97.27</v>
       </c>
-    </row>
-    <row r="132" spans="1:24">
+      <c r="AA131" s="7">
+        <f t="shared" si="25"/>
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="132" spans="1:27">
       <c r="A132" s="1">
         <v>45761</v>
       </c>
@@ -11471,8 +12156,12 @@
       <c r="X132">
         <v>96.9</v>
       </c>
-    </row>
-    <row r="133" spans="1:24">
+      <c r="AA132" s="7">
+        <f t="shared" ref="AA132:AA195" si="26">+AA131+1</f>
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="133" spans="1:27">
       <c r="A133" s="1">
         <v>45762</v>
       </c>
@@ -11545,8 +12234,12 @@
       <c r="X133">
         <v>96.01</v>
       </c>
-    </row>
-    <row r="134" spans="1:24">
+      <c r="AA133" s="7">
+        <f t="shared" si="26"/>
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="134" spans="1:27">
       <c r="A134" s="1">
         <v>45763</v>
       </c>
@@ -11619,8 +12312,12 @@
       <c r="X134">
         <v>95.99</v>
       </c>
-    </row>
-    <row r="135" spans="1:24">
+      <c r="AA134" s="7">
+        <f t="shared" si="26"/>
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="135" spans="1:27">
       <c r="A135" s="1">
         <v>45768</v>
       </c>
@@ -11693,8 +12390,12 @@
       <c r="X135">
         <v>95.7</v>
       </c>
-    </row>
-    <row r="136" spans="1:24">
+      <c r="AA135" s="7">
+        <f t="shared" si="26"/>
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="136" spans="1:27">
       <c r="A136" s="1">
         <v>45769</v>
       </c>
@@ -11767,8 +12468,12 @@
       <c r="X136">
         <v>95.95</v>
       </c>
-    </row>
-    <row r="137" spans="1:24">
+      <c r="AA136" s="7">
+        <f t="shared" si="26"/>
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="137" spans="1:27">
       <c r="A137" s="1">
         <v>45770</v>
       </c>
@@ -11841,8 +12546,12 @@
       <c r="X137">
         <v>96.5</v>
       </c>
-    </row>
-    <row r="138" spans="1:24">
+      <c r="AA137" s="7">
+        <f t="shared" si="26"/>
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="138" spans="1:27">
       <c r="A138" s="1">
         <v>45771</v>
       </c>
@@ -11915,8 +12624,12 @@
       <c r="X138">
         <v>96.4</v>
       </c>
-    </row>
-    <row r="139" spans="1:24">
+      <c r="AA138" s="7">
+        <f t="shared" si="26"/>
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="139" spans="1:27">
       <c r="A139" s="1">
         <v>45772</v>
       </c>
@@ -11989,8 +12702,12 @@
       <c r="X139">
         <v>96.32</v>
       </c>
-    </row>
-    <row r="140" spans="1:24">
+      <c r="AA139" s="7">
+        <f t="shared" si="26"/>
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="140" spans="1:27">
       <c r="A140" s="1">
         <v>45775</v>
       </c>
@@ -12063,8 +12780,12 @@
       <c r="X140">
         <v>96.2</v>
       </c>
-    </row>
-    <row r="141" spans="1:24">
+      <c r="AA140" s="7">
+        <f t="shared" si="26"/>
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="141" spans="1:27">
       <c r="A141" s="1">
         <v>45776</v>
       </c>
@@ -12137,8 +12858,12 @@
       <c r="X141">
         <v>96.2</v>
       </c>
-    </row>
-    <row r="142" spans="1:24">
+      <c r="AA141" s="7">
+        <f t="shared" si="26"/>
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="142" spans="1:27">
       <c r="A142" s="1">
         <v>45777</v>
       </c>
@@ -12211,8 +12936,12 @@
       <c r="X142">
         <v>96.25</v>
       </c>
-    </row>
-    <row r="143" spans="1:24">
+      <c r="AA142" s="7">
+        <f t="shared" si="26"/>
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="143" spans="1:27">
       <c r="A143" s="1">
         <v>45782</v>
       </c>
@@ -12285,8 +13014,12 @@
       <c r="X143">
         <v>96.3</v>
       </c>
-    </row>
-    <row r="144" spans="1:24">
+      <c r="AA143" s="7">
+        <f t="shared" si="26"/>
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="144" spans="1:27">
       <c r="A144" s="1">
         <v>45783</v>
       </c>
@@ -12359,8 +13092,12 @@
       <c r="X144">
         <v>96.5</v>
       </c>
-    </row>
-    <row r="145" spans="1:24">
+      <c r="AA144" s="7">
+        <f t="shared" si="26"/>
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="145" spans="1:27">
       <c r="A145" s="1">
         <v>45784</v>
       </c>
@@ -12433,8 +13170,12 @@
       <c r="X145">
         <v>96.45</v>
       </c>
-    </row>
-    <row r="146" spans="1:24">
+      <c r="AA145" s="7">
+        <f t="shared" si="26"/>
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="146" spans="1:27">
       <c r="A146" s="1">
         <v>45785</v>
       </c>
@@ -12507,8 +13248,12 @@
       <c r="X146">
         <v>96.8</v>
       </c>
-    </row>
-    <row r="147" spans="1:24">
+      <c r="AA146" s="7">
+        <f t="shared" si="26"/>
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="147" spans="1:27">
       <c r="A147" s="1">
         <v>45786</v>
       </c>
@@ -12581,8 +13326,12 @@
       <c r="X147">
         <v>97.61</v>
       </c>
-    </row>
-    <row r="148" spans="1:24">
+      <c r="AA147" s="7">
+        <f t="shared" si="26"/>
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="148" spans="1:27">
       <c r="A148" s="1">
         <v>45789</v>
       </c>
@@ -12655,8 +13404,12 @@
       <c r="X148">
         <v>97.65</v>
       </c>
-    </row>
-    <row r="149" spans="1:24">
+      <c r="AA148" s="7">
+        <f t="shared" si="26"/>
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="149" spans="1:27">
       <c r="A149" s="1">
         <v>45790</v>
       </c>
@@ -12729,8 +13482,12 @@
       <c r="X149">
         <v>97.55</v>
       </c>
-    </row>
-    <row r="150" spans="1:24">
+      <c r="AA149" s="7">
+        <f t="shared" si="26"/>
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="150" spans="1:27">
       <c r="A150" s="1">
         <v>45791</v>
       </c>
@@ -12803,8 +13560,12 @@
       <c r="X150">
         <v>97.75</v>
       </c>
-    </row>
-    <row r="151" spans="1:24">
+      <c r="AA150" s="7">
+        <f t="shared" si="26"/>
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="151" spans="1:27">
       <c r="A151" s="1">
         <v>45792</v>
       </c>
@@ -12877,8 +13638,12 @@
       <c r="X151">
         <v>97.9</v>
       </c>
-    </row>
-    <row r="152" spans="1:24">
+      <c r="AA151" s="7">
+        <f t="shared" si="26"/>
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="152" spans="1:27">
       <c r="A152" s="1">
         <v>45793</v>
       </c>
@@ -12951,8 +13716,12 @@
       <c r="X152">
         <v>97.55</v>
       </c>
-    </row>
-    <row r="153" spans="1:24">
+      <c r="AA152" s="7">
+        <f t="shared" si="26"/>
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="153" spans="1:27">
       <c r="A153" s="1">
         <v>45796</v>
       </c>
@@ -13025,8 +13794,12 @@
       <c r="X153">
         <v>97.6</v>
       </c>
-    </row>
-    <row r="154" spans="1:24">
+      <c r="AA153" s="7">
+        <f t="shared" si="26"/>
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="154" spans="1:27">
       <c r="A154" s="1">
         <v>45797</v>
       </c>
@@ -13099,8 +13872,12 @@
       <c r="X154">
         <v>97.66</v>
       </c>
-    </row>
-    <row r="155" spans="1:24">
+      <c r="AA154" s="7">
+        <f t="shared" si="26"/>
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="155" spans="1:27">
       <c r="A155" s="1">
         <v>45798</v>
       </c>
@@ -13173,8 +13950,12 @@
       <c r="X155">
         <v>97.5</v>
       </c>
-    </row>
-    <row r="156" spans="1:24">
+      <c r="AA155" s="7">
+        <f t="shared" si="26"/>
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="156" spans="1:27">
       <c r="A156" s="1">
         <v>45799</v>
       </c>
@@ -13247,8 +14028,12 @@
       <c r="X156">
         <v>97.3</v>
       </c>
-    </row>
-    <row r="157" spans="1:24">
+      <c r="AA156" s="7">
+        <f t="shared" si="26"/>
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="157" spans="1:27">
       <c r="A157" s="1">
         <v>45800</v>
       </c>
@@ -13321,8 +14106,12 @@
       <c r="X157">
         <v>97.6</v>
       </c>
-    </row>
-    <row r="158" spans="1:24">
+      <c r="AA157" s="7">
+        <f t="shared" si="26"/>
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="158" spans="1:27">
       <c r="A158" s="1">
         <v>45803</v>
       </c>
@@ -13395,8 +14184,12 @@
       <c r="X158">
         <v>97.99</v>
       </c>
-    </row>
-    <row r="159" spans="1:24">
+      <c r="AA158" s="7">
+        <f t="shared" si="26"/>
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="159" spans="1:27">
       <c r="A159" s="1">
         <v>45804</v>
       </c>
@@ -13469,8 +14262,12 @@
       <c r="X159">
         <v>98</v>
       </c>
-    </row>
-    <row r="160" spans="1:24">
+      <c r="AA159" s="7">
+        <f t="shared" si="26"/>
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="160" spans="1:27">
       <c r="A160" s="1">
         <v>45805</v>
       </c>
@@ -13543,8 +14340,12 @@
       <c r="X160">
         <v>98.6</v>
       </c>
-    </row>
-    <row r="161" spans="1:24">
+      <c r="AA160" s="7">
+        <f t="shared" si="26"/>
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="161" spans="1:27">
       <c r="A161" s="1">
         <v>45806</v>
       </c>
@@ -13617,8 +14418,12 @@
       <c r="X161">
         <v>98.6</v>
       </c>
-    </row>
-    <row r="162" spans="1:24">
+      <c r="AA161" s="7">
+        <f t="shared" si="26"/>
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="162" spans="1:27">
       <c r="A162" s="1">
         <v>45807</v>
       </c>
@@ -13691,8 +14496,12 @@
       <c r="X162">
         <v>98.65</v>
       </c>
-    </row>
-    <row r="163" spans="1:24">
+      <c r="AA162" s="7">
+        <f t="shared" si="26"/>
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="163" spans="1:27">
       <c r="A163" s="1">
         <v>45810</v>
       </c>
@@ -13765,8 +14574,12 @@
       <c r="X163">
         <v>98.9</v>
       </c>
-    </row>
-    <row r="164" spans="1:24">
+      <c r="AA163" s="7">
+        <f t="shared" si="26"/>
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="164" spans="1:27">
       <c r="A164" s="1">
         <v>45811</v>
       </c>
@@ -13839,8 +14652,12 @@
       <c r="X164">
         <v>98.7</v>
       </c>
-    </row>
-    <row r="165" spans="1:24">
+      <c r="AA164" s="7">
+        <f t="shared" si="26"/>
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="165" spans="1:27">
       <c r="A165" s="1">
         <v>45812</v>
       </c>
@@ -13913,8 +14730,12 @@
       <c r="X165">
         <v>98.6</v>
       </c>
-    </row>
-    <row r="166" spans="1:24">
+      <c r="AA165" s="7">
+        <f t="shared" si="26"/>
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="166" spans="1:27">
       <c r="A166" s="1">
         <v>45813</v>
       </c>
@@ -13987,8 +14808,12 @@
       <c r="X166">
         <v>98.6</v>
       </c>
-    </row>
-    <row r="167" spans="1:24">
+      <c r="AA166" s="7">
+        <f t="shared" si="26"/>
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="167" spans="1:27">
       <c r="A167" s="1">
         <v>45814</v>
       </c>
@@ -14061,8 +14886,12 @@
       <c r="X167">
         <v>98.6</v>
       </c>
-    </row>
-    <row r="168" spans="1:24">
+      <c r="AA167" s="7">
+        <f t="shared" si="26"/>
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="168" spans="1:27">
       <c r="A168" s="1">
         <v>45817</v>
       </c>
@@ -14135,8 +14964,12 @@
       <c r="X168">
         <v>98.55</v>
       </c>
-    </row>
-    <row r="169" spans="1:24">
+      <c r="AA168" s="7">
+        <f t="shared" si="26"/>
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="169" spans="1:27">
       <c r="A169" s="1">
         <v>45818</v>
       </c>
@@ -14209,8 +15042,12 @@
       <c r="X169">
         <v>98.6</v>
       </c>
-    </row>
-    <row r="170" spans="1:24">
+      <c r="AA169" s="7">
+        <f t="shared" si="26"/>
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="170" spans="1:27">
       <c r="A170" s="1">
         <v>45819</v>
       </c>
@@ -14283,8 +15120,12 @@
       <c r="X170">
         <v>98.7</v>
       </c>
-    </row>
-    <row r="171" spans="1:24">
+      <c r="AA170" s="7">
+        <f t="shared" si="26"/>
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="171" spans="1:27">
       <c r="A171" s="1">
         <v>45820</v>
       </c>
@@ -14357,8 +15198,12 @@
       <c r="X171">
         <v>98.56</v>
       </c>
-    </row>
-    <row r="172" spans="1:24">
+      <c r="AA171" s="7">
+        <f t="shared" si="26"/>
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="172" spans="1:27">
       <c r="A172" s="1">
         <v>45821</v>
       </c>
@@ -14431,8 +15276,12 @@
       <c r="X172">
         <v>98.66</v>
       </c>
-    </row>
-    <row r="173" spans="1:24">
+      <c r="AA172" s="7">
+        <f t="shared" si="26"/>
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="173" spans="1:27">
       <c r="A173" s="1">
         <v>45825</v>
       </c>
@@ -14505,8 +15354,12 @@
       <c r="X173">
         <v>98.65</v>
       </c>
-    </row>
-    <row r="174" spans="1:24">
+      <c r="AA173" s="7">
+        <f t="shared" si="26"/>
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="174" spans="1:27">
       <c r="A174" s="1">
         <v>45826</v>
       </c>
@@ -14579,8 +15432,12 @@
       <c r="X174">
         <v>98.6</v>
       </c>
-    </row>
-    <row r="175" spans="1:24">
+      <c r="AA174" s="7">
+        <f t="shared" si="26"/>
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="175" spans="1:27">
       <c r="A175" s="1">
         <v>45827</v>
       </c>
@@ -14653,8 +15510,12 @@
       <c r="X175">
         <v>98.69</v>
       </c>
-    </row>
-    <row r="176" spans="1:24">
+      <c r="AA175" s="7">
+        <f t="shared" si="26"/>
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="176" spans="1:27">
       <c r="A176" s="1">
         <v>45831</v>
       </c>
@@ -14727,8 +15588,12 @@
       <c r="X176">
         <v>98.69</v>
       </c>
-    </row>
-    <row r="177" spans="1:26">
+      <c r="AA176" s="7">
+        <f t="shared" si="26"/>
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="177" spans="1:27">
       <c r="A177" s="1">
         <v>45832</v>
       </c>
@@ -14801,8 +15666,12 @@
       <c r="X177">
         <v>98.69</v>
       </c>
-    </row>
-    <row r="178" spans="1:26">
+      <c r="AA177" s="7">
+        <f t="shared" si="26"/>
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="178" spans="1:27">
       <c r="A178" s="1">
         <v>45833</v>
       </c>
@@ -14875,8 +15744,12 @@
       <c r="X178">
         <v>98.69</v>
       </c>
-    </row>
-    <row r="179" spans="1:26">
+      <c r="AA178" s="7">
+        <f t="shared" si="26"/>
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="179" spans="1:27">
       <c r="A179" s="1">
         <v>45834</v>
       </c>
@@ -14949,8 +15822,12 @@
       <c r="X179">
         <v>98.69</v>
       </c>
-    </row>
-    <row r="180" spans="1:26">
+      <c r="AA179" s="7">
+        <f t="shared" si="26"/>
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="180" spans="1:27">
       <c r="A180" s="1">
         <v>45835</v>
       </c>
@@ -15029,8 +15906,12 @@
       <c r="Z180">
         <v>0</v>
       </c>
-    </row>
-    <row r="181" spans="1:26">
+      <c r="AA180" s="7">
+        <f t="shared" si="26"/>
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="181" spans="1:27">
       <c r="A181" s="1">
         <v>45838</v>
       </c>
@@ -15109,8 +15990,12 @@
       <c r="Z181">
         <v>84</v>
       </c>
-    </row>
-    <row r="182" spans="1:26">
+      <c r="AA181" s="7">
+        <f t="shared" si="26"/>
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="182" spans="1:27">
       <c r="A182" s="1">
         <v>45839</v>
       </c>
@@ -15186,8 +16071,12 @@
       <c r="Z182">
         <v>80.5</v>
       </c>
-    </row>
-    <row r="183" spans="1:26">
+      <c r="AA182" s="7">
+        <f t="shared" si="26"/>
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="183" spans="1:27">
       <c r="A183" s="1">
         <v>45840</v>
       </c>
@@ -15266,8 +16155,12 @@
       <c r="Z183">
         <v>82</v>
       </c>
-    </row>
-    <row r="184" spans="1:26">
+      <c r="AA183" s="7">
+        <f t="shared" si="26"/>
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="184" spans="1:27">
       <c r="A184" s="1">
         <v>45841</v>
       </c>
@@ -15346,8 +16239,12 @@
       <c r="Z184">
         <v>82.4</v>
       </c>
-    </row>
-    <row r="185" spans="1:26">
+      <c r="AA184" s="7">
+        <f t="shared" si="26"/>
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="185" spans="1:27">
       <c r="A185" s="1">
         <v>45842</v>
       </c>
@@ -15426,8 +16323,12 @@
       <c r="Z185">
         <v>83.5</v>
       </c>
-    </row>
-    <row r="186" spans="1:26">
+      <c r="AA185" s="7">
+        <f t="shared" si="26"/>
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="186" spans="1:27">
       <c r="A186" s="1">
         <v>45845</v>
       </c>
@@ -15506,8 +16407,12 @@
       <c r="Z186">
         <v>81.900000000000006</v>
       </c>
-    </row>
-    <row r="187" spans="1:26">
+      <c r="AA186" s="7">
+        <f t="shared" si="26"/>
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="187" spans="1:27">
       <c r="A187" s="1">
         <v>45846</v>
       </c>
@@ -15586,8 +16491,12 @@
       <c r="Z187">
         <v>82</v>
       </c>
-    </row>
-    <row r="188" spans="1:26">
+      <c r="AA187" s="7">
+        <f t="shared" si="26"/>
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="188" spans="1:27">
       <c r="A188" s="1">
         <v>45848</v>
       </c>
@@ -15666,8 +16575,12 @@
       <c r="Z188">
         <v>81.8</v>
       </c>
-    </row>
-    <row r="189" spans="1:26">
+      <c r="AA188" s="7">
+        <f t="shared" si="26"/>
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="189" spans="1:27">
       <c r="A189" s="1">
         <v>45849</v>
       </c>
@@ -15746,8 +16659,12 @@
       <c r="Z189">
         <v>81.900000000000006</v>
       </c>
-    </row>
-    <row r="190" spans="1:26">
+      <c r="AA189" s="7">
+        <f t="shared" si="26"/>
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="190" spans="1:27">
       <c r="A190" s="1">
         <v>45852</v>
       </c>
@@ -15826,8 +16743,12 @@
       <c r="Z190">
         <v>81.5</v>
       </c>
-    </row>
-    <row r="191" spans="1:26">
+      <c r="AA190" s="7">
+        <f t="shared" si="26"/>
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="191" spans="1:27">
       <c r="A191" s="1">
         <v>45853</v>
       </c>
@@ -15906,8 +16827,12 @@
       <c r="Z191">
         <v>81.400000000000006</v>
       </c>
-    </row>
-    <row r="192" spans="1:26">
+      <c r="AA191" s="7">
+        <f t="shared" si="26"/>
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="192" spans="1:27">
       <c r="A192" s="1">
         <v>45854</v>
       </c>
@@ -15986,8 +16911,12 @@
       <c r="Z192">
         <v>81.3</v>
       </c>
-    </row>
-    <row r="193" spans="1:26">
+      <c r="AA192" s="7">
+        <f t="shared" si="26"/>
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="193" spans="1:27">
       <c r="A193" s="1">
         <v>45855</v>
       </c>
@@ -16066,8 +16995,12 @@
       <c r="Z193">
         <v>81.099999999999994</v>
       </c>
-    </row>
-    <row r="194" spans="1:26">
+      <c r="AA193" s="7">
+        <f t="shared" si="26"/>
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="194" spans="1:27">
       <c r="A194" s="1">
         <v>45856</v>
       </c>
@@ -16146,8 +17079,12 @@
       <c r="Z194">
         <v>81.05</v>
       </c>
-    </row>
-    <row r="195" spans="1:26">
+      <c r="AA194" s="7">
+        <f t="shared" si="26"/>
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="195" spans="1:27">
       <c r="A195" s="1">
         <v>45859</v>
       </c>
@@ -16226,8 +17163,12 @@
       <c r="Z195">
         <v>81.150000000000006</v>
       </c>
-    </row>
-    <row r="196" spans="1:26">
+      <c r="AA195" s="7">
+        <f t="shared" si="26"/>
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="196" spans="1:27">
       <c r="A196" s="1">
         <v>45860</v>
       </c>
@@ -16306,8 +17247,12 @@
       <c r="Z196">
         <v>80.94</v>
       </c>
-    </row>
-    <row r="197" spans="1:26">
+      <c r="AA196" s="7">
+        <f t="shared" ref="AA196:AA250" si="27">+AA195+1</f>
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="197" spans="1:27">
       <c r="A197" s="1">
         <v>45861</v>
       </c>
@@ -16386,8 +17331,12 @@
       <c r="Z197">
         <v>80.47</v>
       </c>
-    </row>
-    <row r="198" spans="1:26">
+      <c r="AA197" s="7">
+        <f t="shared" si="27"/>
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="198" spans="1:27">
       <c r="A198" s="1">
         <v>45862</v>
       </c>
@@ -16466,8 +17415,12 @@
       <c r="Z198">
         <v>80.400000000000006</v>
       </c>
-    </row>
-    <row r="199" spans="1:26">
+      <c r="AA198" s="7">
+        <f t="shared" si="27"/>
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="199" spans="1:27">
       <c r="A199" s="1">
         <v>45863</v>
       </c>
@@ -16546,8 +17499,12 @@
       <c r="Z199">
         <v>80.28</v>
       </c>
-    </row>
-    <row r="200" spans="1:26">
+      <c r="AA199" s="7">
+        <f t="shared" si="27"/>
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="200" spans="1:27">
       <c r="A200" s="1">
         <v>45866</v>
       </c>
@@ -16626,8 +17583,12 @@
       <c r="Z200">
         <v>80.400000000000006</v>
       </c>
-    </row>
-    <row r="201" spans="1:26">
+      <c r="AA200" s="7">
+        <f t="shared" si="27"/>
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="201" spans="1:27">
       <c r="A201" s="1">
         <v>45867</v>
       </c>
@@ -16706,8 +17667,12 @@
       <c r="Z201">
         <v>80.45</v>
       </c>
-    </row>
-    <row r="202" spans="1:26">
+      <c r="AA201" s="7">
+        <f t="shared" si="27"/>
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="202" spans="1:27">
       <c r="A202" s="1">
         <v>45868</v>
       </c>
@@ -16786,8 +17751,12 @@
       <c r="Z202">
         <v>80.400000000000006</v>
       </c>
-    </row>
-    <row r="203" spans="1:26">
+      <c r="AA202" s="7">
+        <f t="shared" si="27"/>
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="203" spans="1:27">
       <c r="A203" s="1">
         <v>45869</v>
       </c>
@@ -16866,8 +17835,12 @@
       <c r="Z203">
         <v>80.209999999999994</v>
       </c>
-    </row>
-    <row r="204" spans="1:26">
+      <c r="AA203" s="7">
+        <f t="shared" si="27"/>
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="204" spans="1:27">
       <c r="A204" s="1">
         <v>45870</v>
       </c>
@@ -16946,8 +17919,12 @@
       <c r="Z204">
         <v>80.09</v>
       </c>
-    </row>
-    <row r="205" spans="1:26">
+      <c r="AA204" s="7">
+        <f t="shared" si="27"/>
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="205" spans="1:27">
       <c r="A205" s="1">
         <v>45873</v>
       </c>
@@ -17026,8 +18003,12 @@
       <c r="Z205">
         <v>80.099999999999994</v>
       </c>
-    </row>
-    <row r="206" spans="1:26">
+      <c r="AA205" s="7">
+        <f t="shared" si="27"/>
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="206" spans="1:27">
       <c r="A206" s="1">
         <v>45874</v>
       </c>
@@ -17106,8 +18087,12 @@
       <c r="Z206">
         <v>80.2</v>
       </c>
-    </row>
-    <row r="207" spans="1:26">
+      <c r="AA206" s="7">
+        <f t="shared" si="27"/>
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="207" spans="1:27">
       <c r="A207" s="1">
         <v>45875</v>
       </c>
@@ -17186,8 +18171,12 @@
       <c r="Z207">
         <v>80.05</v>
       </c>
-    </row>
-    <row r="208" spans="1:26">
+      <c r="AA207" s="7">
+        <f t="shared" si="27"/>
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="208" spans="1:27">
       <c r="A208" s="1">
         <v>45876</v>
       </c>
@@ -17266,8 +18255,12 @@
       <c r="Z208">
         <v>80</v>
       </c>
-    </row>
-    <row r="209" spans="1:26">
+      <c r="AA208" s="7">
+        <f t="shared" si="27"/>
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="209" spans="1:27">
       <c r="A209" s="1">
         <v>45877</v>
       </c>
@@ -17346,8 +18339,12 @@
       <c r="Z209">
         <v>79.7</v>
       </c>
-    </row>
-    <row r="210" spans="1:26">
+      <c r="AA209" s="7">
+        <f t="shared" si="27"/>
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="210" spans="1:27">
       <c r="A210" s="1">
         <v>45880</v>
       </c>
@@ -17426,8 +18423,12 @@
       <c r="Z210">
         <v>80.2</v>
       </c>
-    </row>
-    <row r="211" spans="1:26">
+      <c r="AA210" s="7">
+        <f t="shared" si="27"/>
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="211" spans="1:27">
       <c r="A211" s="1">
         <v>45881</v>
       </c>
@@ -17506,8 +18507,12 @@
       <c r="Z211">
         <v>79.75</v>
       </c>
-    </row>
-    <row r="212" spans="1:26">
+      <c r="AA211" s="7">
+        <f t="shared" si="27"/>
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="212" spans="1:27">
       <c r="A212" s="1">
         <v>45882</v>
       </c>
@@ -17586,8 +18591,12 @@
       <c r="Z212">
         <v>79.73</v>
       </c>
-    </row>
-    <row r="213" spans="1:26">
+      <c r="AA212" s="7">
+        <f t="shared" si="27"/>
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="213" spans="1:27">
       <c r="A213" s="1">
         <v>45883</v>
       </c>
@@ -17666,8 +18675,12 @@
       <c r="Z213">
         <v>79.5</v>
       </c>
-    </row>
-    <row r="214" spans="1:26">
+      <c r="AA213" s="7">
+        <f t="shared" si="27"/>
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="214" spans="1:27">
       <c r="A214" s="1">
         <v>45887</v>
       </c>
@@ -17746,8 +18759,12 @@
       <c r="Z214">
         <v>79.61</v>
       </c>
-    </row>
-    <row r="215" spans="1:26">
+      <c r="AA214" s="7">
+        <f t="shared" si="27"/>
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="215" spans="1:27">
       <c r="A215" s="1">
         <v>45888</v>
       </c>
@@ -17826,8 +18843,12 @@
       <c r="Z215">
         <v>79.63</v>
       </c>
-    </row>
-    <row r="216" spans="1:26">
+      <c r="AA215" s="7">
+        <f t="shared" si="27"/>
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="216" spans="1:27">
       <c r="A216" s="1">
         <v>45889</v>
       </c>
@@ -17906,8 +18927,12 @@
       <c r="Z216">
         <v>79.599999999999994</v>
       </c>
-    </row>
-    <row r="217" spans="1:26">
+      <c r="AA216" s="7">
+        <f t="shared" si="27"/>
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="217" spans="1:27">
       <c r="A217" s="1">
         <v>45890</v>
       </c>
@@ -17986,8 +19011,12 @@
       <c r="Z217">
         <v>79.599999999999994</v>
       </c>
-    </row>
-    <row r="218" spans="1:26">
+      <c r="AA217" s="7">
+        <f t="shared" si="27"/>
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="218" spans="1:27">
       <c r="A218" s="1">
         <v>45891</v>
       </c>
@@ -18066,8 +19095,12 @@
       <c r="Z218">
         <v>79.42</v>
       </c>
-    </row>
-    <row r="219" spans="1:26">
+      <c r="AA218" s="7">
+        <f t="shared" si="27"/>
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="219" spans="1:27">
       <c r="A219" s="1">
         <v>45894</v>
       </c>
@@ -18146,8 +19179,12 @@
       <c r="Z219">
         <v>78.8</v>
       </c>
-    </row>
-    <row r="220" spans="1:26">
+      <c r="AA219" s="7">
+        <f t="shared" si="27"/>
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="220" spans="1:27">
       <c r="A220" s="1">
         <v>45895</v>
       </c>
@@ -18226,8 +19263,12 @@
       <c r="Z220">
         <v>78.5</v>
       </c>
-    </row>
-    <row r="221" spans="1:26">
+      <c r="AA220" s="7">
+        <f t="shared" si="27"/>
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="221" spans="1:27">
       <c r="A221" s="1">
         <v>45896</v>
       </c>
@@ -18306,8 +19347,12 @@
       <c r="Z221">
         <v>77.010000000000005</v>
       </c>
-    </row>
-    <row r="222" spans="1:26">
+      <c r="AA221" s="7">
+        <f t="shared" si="27"/>
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="222" spans="1:27">
       <c r="A222" s="1">
         <v>45897</v>
       </c>
@@ -18386,8 +19431,12 @@
       <c r="Z222">
         <v>77.3</v>
       </c>
-    </row>
-    <row r="223" spans="1:26">
+      <c r="AA222" s="7">
+        <f t="shared" si="27"/>
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="223" spans="1:27">
       <c r="A223" s="1">
         <v>45898</v>
       </c>
@@ -18466,8 +19515,12 @@
       <c r="Z223">
         <v>77.25</v>
       </c>
-    </row>
-    <row r="224" spans="1:26">
+      <c r="AA223" s="7">
+        <f t="shared" si="27"/>
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="224" spans="1:27">
       <c r="A224" s="1">
         <v>45901</v>
       </c>
@@ -18546,8 +19599,12 @@
       <c r="Z224">
         <v>77</v>
       </c>
-    </row>
-    <row r="225" spans="1:26">
+      <c r="AA224" s="7">
+        <f t="shared" si="27"/>
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="225" spans="1:27">
       <c r="A225" s="1">
         <v>45902</v>
       </c>
@@ -18626,8 +19683,12 @@
       <c r="Z225">
         <v>75.97</v>
       </c>
-    </row>
-    <row r="226" spans="1:26">
+      <c r="AA225" s="7">
+        <f t="shared" si="27"/>
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="226" spans="1:27">
       <c r="A226" s="1">
         <v>45903</v>
       </c>
@@ -18706,8 +19767,12 @@
       <c r="Z226">
         <v>75.55</v>
       </c>
-    </row>
-    <row r="227" spans="1:26">
+      <c r="AA226" s="7">
+        <f t="shared" si="27"/>
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="227" spans="1:27">
       <c r="A227" s="1">
         <v>45904</v>
       </c>
@@ -18786,8 +19851,12 @@
       <c r="Z227">
         <v>75.2</v>
       </c>
-    </row>
-    <row r="228" spans="1:26">
+      <c r="AA227" s="7">
+        <f t="shared" si="27"/>
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="228" spans="1:27">
       <c r="A228" s="1">
         <v>45905</v>
       </c>
@@ -18866,8 +19935,12 @@
       <c r="Z228">
         <v>74.650000000000006</v>
       </c>
-    </row>
-    <row r="229" spans="1:26">
+      <c r="AA228" s="7">
+        <f t="shared" si="27"/>
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="229" spans="1:27">
       <c r="A229" s="1">
         <v>45908</v>
       </c>
@@ -18946,8 +20019,12 @@
       <c r="Z229">
         <v>70.5</v>
       </c>
-    </row>
-    <row r="230" spans="1:26">
+      <c r="AA229" s="7">
+        <f t="shared" si="27"/>
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="230" spans="1:27">
       <c r="A230" s="1">
         <v>45909</v>
       </c>
@@ -19026,8 +20103,12 @@
       <c r="Z230">
         <v>70.5</v>
       </c>
-    </row>
-    <row r="231" spans="1:26">
+      <c r="AA230" s="7">
+        <f t="shared" si="27"/>
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="231" spans="1:27">
       <c r="A231" s="1">
         <v>45910</v>
       </c>
@@ -19106,8 +20187,12 @@
       <c r="Z231">
         <v>70.3</v>
       </c>
-    </row>
-    <row r="232" spans="1:26">
+      <c r="AA231" s="7">
+        <f t="shared" si="27"/>
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="232" spans="1:27">
       <c r="A232" s="1">
         <v>45911</v>
       </c>
@@ -19186,8 +20271,12 @@
       <c r="Z232">
         <v>70.02</v>
       </c>
-    </row>
-    <row r="233" spans="1:26">
+      <c r="AA232" s="7">
+        <f t="shared" si="27"/>
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="233" spans="1:27">
       <c r="A233" s="1">
         <v>45912</v>
       </c>
@@ -19266,8 +20355,12 @@
       <c r="Z233">
         <v>68.5</v>
       </c>
-    </row>
-    <row r="234" spans="1:26">
+      <c r="AA233" s="7">
+        <f t="shared" si="27"/>
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="234" spans="1:27">
       <c r="A234" s="1">
         <v>45915</v>
       </c>
@@ -19346,8 +20439,12 @@
       <c r="Z234">
         <v>66.5</v>
       </c>
-    </row>
-    <row r="235" spans="1:26">
+      <c r="AA234" s="7">
+        <f t="shared" si="27"/>
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="235" spans="1:27">
       <c r="A235" s="1">
         <v>45916</v>
       </c>
@@ -19426,8 +20523,12 @@
       <c r="Z235">
         <v>66.5</v>
       </c>
-    </row>
-    <row r="236" spans="1:26">
+      <c r="AA235" s="7">
+        <f t="shared" si="27"/>
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="236" spans="1:27">
       <c r="A236" s="1">
         <v>45917</v>
       </c>
@@ -19506,8 +20607,12 @@
       <c r="Z236">
         <v>65.25</v>
       </c>
-    </row>
-    <row r="237" spans="1:26">
+      <c r="AA236" s="7">
+        <f t="shared" si="27"/>
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="237" spans="1:27">
       <c r="A237" s="1">
         <v>45918</v>
       </c>
@@ -19586,8 +20691,12 @@
       <c r="Z237">
         <v>58.52</v>
       </c>
-    </row>
-    <row r="238" spans="1:26">
+      <c r="AA237" s="7">
+        <f t="shared" si="27"/>
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="238" spans="1:27">
       <c r="A238" s="1">
         <v>45919</v>
       </c>
@@ -19666,8 +20775,12 @@
       <c r="Z238">
         <v>55.33</v>
       </c>
-    </row>
-    <row r="239" spans="1:26">
+      <c r="AA238" s="7">
+        <f t="shared" si="27"/>
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="239" spans="1:27">
       <c r="A239" s="1">
         <v>45922</v>
       </c>
@@ -19746,8 +20859,12 @@
       <c r="Z239">
         <v>63.5</v>
       </c>
-    </row>
-    <row r="240" spans="1:26">
+      <c r="AA239" s="7">
+        <f t="shared" si="27"/>
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="240" spans="1:27">
       <c r="A240" s="1">
         <v>45923</v>
       </c>
@@ -19826,8 +20943,12 @@
       <c r="Z240">
         <v>69</v>
       </c>
-    </row>
-    <row r="241" spans="1:26">
+      <c r="AA240" s="7">
+        <f t="shared" si="27"/>
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="241" spans="1:27">
       <c r="A241" s="1">
         <v>45924</v>
       </c>
@@ -19906,8 +21027,12 @@
       <c r="Z241">
         <v>68.59</v>
       </c>
-    </row>
-    <row r="242" spans="1:26">
+      <c r="AA241" s="7">
+        <f t="shared" si="27"/>
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="242" spans="1:27">
       <c r="A242" s="1">
         <v>45925</v>
       </c>
@@ -19986,8 +21111,12 @@
       <c r="Z242">
         <v>66.5</v>
       </c>
-    </row>
-    <row r="243" spans="1:26">
+      <c r="AA242" s="7">
+        <f t="shared" si="27"/>
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="243" spans="1:27">
       <c r="A243" s="1">
         <v>45926</v>
       </c>
@@ -20066,8 +21195,12 @@
       <c r="Z243">
         <v>65.67</v>
       </c>
-    </row>
-    <row r="244" spans="1:26">
+      <c r="AA243" s="7">
+        <f t="shared" si="27"/>
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="244" spans="1:27">
       <c r="A244" s="1">
         <v>45929</v>
       </c>
@@ -20146,8 +21279,12 @@
       <c r="Z244">
         <v>65.67</v>
       </c>
-    </row>
-    <row r="245" spans="1:26">
+      <c r="AA244" s="7">
+        <f t="shared" si="27"/>
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="245" spans="1:27">
       <c r="A245" s="1">
         <v>45930</v>
       </c>
@@ -20226,8 +21363,12 @@
       <c r="Z245">
         <v>65.67</v>
       </c>
-    </row>
-    <row r="246" spans="1:26">
+      <c r="AA245" s="7">
+        <f t="shared" si="27"/>
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="246" spans="1:27">
       <c r="A246" s="1">
         <v>45931</v>
       </c>
@@ -20306,8 +21447,12 @@
       <c r="Z246">
         <v>65.67</v>
       </c>
-    </row>
-    <row r="247" spans="1:26">
+      <c r="AA246" s="7">
+        <f t="shared" si="27"/>
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="247" spans="1:27">
       <c r="A247" s="1">
         <v>45932</v>
       </c>
@@ -20386,8 +21531,12 @@
       <c r="Z247">
         <v>65.67</v>
       </c>
-    </row>
-    <row r="248" spans="1:26">
+      <c r="AA247" s="7">
+        <f t="shared" si="27"/>
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="248" spans="1:27">
       <c r="A248" s="1">
         <v>45933</v>
       </c>
@@ -20466,8 +21615,12 @@
       <c r="Z248">
         <v>65.67</v>
       </c>
-    </row>
-    <row r="249" spans="1:26" s="6" customFormat="1">
+      <c r="AA248" s="7">
+        <f t="shared" si="27"/>
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="249" spans="1:27" s="6" customFormat="1">
       <c r="A249" s="5">
         <v>46098</v>
       </c>
@@ -20546,8 +21699,12 @@
       <c r="Z249" s="6">
         <v>65.67</v>
       </c>
-    </row>
-    <row r="250" spans="1:26" s="6" customFormat="1">
+      <c r="AA249" s="7">
+        <f t="shared" si="27"/>
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="250" spans="1:27" s="6" customFormat="1">
       <c r="A250" s="5">
         <v>46099</v>
       </c>
@@ -20625,6 +21782,10 @@
       </c>
       <c r="Z250" s="6">
         <v>65.67</v>
+      </c>
+      <c r="AA250" s="7">
+        <f t="shared" si="27"/>
+        <v>1380</v>
       </c>
     </row>
   </sheetData>

--- a/operaciones.xlsx
+++ b/operaciones.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A94F1DE1-C542-4319-9537-EEACE9C22FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A25E5DC-CA66-4E22-9F34-E1391A2023CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="45">
   <si>
     <t>Fecha</t>
   </si>
@@ -97,10 +97,10 @@
     <t>AL35</t>
   </si>
   <si>
-    <t>GD35</t>
+    <t>Amortización</t>
   </si>
   <si>
-    <t>Amortización</t>
+    <t>GD35</t>
   </si>
   <si>
     <t>Cupon</t>
@@ -745,19 +745,22 @@
         <f>G4*VLOOKUP(A4,Precios!$A$3:$AA$601,27)</f>
         <v>24157680</v>
       </c>
+      <c r="M4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="1">
-        <v>45978</v>
+        <v>45613</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5">
         <v>100</v>
@@ -771,11 +774,11 @@
       </c>
       <c r="H5" s="8">
         <f>F5*VLOOKUP(A5,Precios!$A$3:$AA$601,27)</f>
-        <v>68900</v>
+        <v>58250</v>
       </c>
       <c r="I5" s="8">
         <f>G5*VLOOKUP(A5,Precios!$A$3:$AA$601,27)</f>
-        <v>6890000</v>
+        <v>5825000</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -847,7 +850,7 @@
         <v>45665</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
@@ -872,13 +875,13 @@
         <v>45665</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G9" s="9">
         <v>8000</v>
@@ -1082,7 +1085,7 @@
         <v>45846</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
@@ -1352,7 +1355,7 @@
         <v>45914</v>
       </c>
       <c r="B25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
         <v>13</v>
@@ -1414,7 +1417,7 @@
     <sortCondition ref="A2:A17"/>
   </sortState>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B11 B15:B37" xr:uid="{D82FC90E-F4C1-4FEE-90A7-1E7B4FF2C652}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B11 B15:B37 M4" xr:uid="{D82FC90E-F4C1-4FEE-90A7-1E7B4FF2C652}">
       <formula1>$M$1:$M$23</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1" xr:uid="{9837364A-ACA4-4040-937F-F0F8B099CD79}">
@@ -1456,7 +1459,7 @@
         <v>24</v>
       </c>
       <c r="D1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1" t="s">
         <v>25</v>

--- a/operaciones.xlsx
+++ b/operaciones.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A25E5DC-CA66-4E22-9F34-E1391A2023CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C42F7B1-9591-40C1-A0B3-4185FED74B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="46">
   <si>
     <t>Fecha</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>Valor ARS</t>
+  </si>
+  <si>
+    <t>Monto cash</t>
   </si>
   <si>
     <t xml:space="preserve">Compra </t>
@@ -574,6 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:S37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -586,7 +590,8 @@
     <col min="7" max="7" width="15.5703125" style="9" customWidth="1"/>
     <col min="8" max="8" width="12.140625" style="9" customWidth="1"/>
     <col min="9" max="9" width="14.140625" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" customWidth="1"/>
     <col min="13" max="13" width="13.28515625" customWidth="1"/>
     <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -594,7 +599,7 @@
     <col min="19" max="19" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -622,28 +627,34 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="M1" t="s">
+      <c r="K1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="O1" t="s">
+      <c r="N1" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="P1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" ht="18" customHeight="1">
+      <c r="R1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="18" customHeight="1">
       <c r="A2" s="1">
         <v>45581</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2">
         <v>1000</v>
@@ -663,28 +674,35 @@
         <f>G2*VLOOKUP(A2,Precios!$A$3:$AA$601,27)</f>
         <v>72369440</v>
       </c>
-      <c r="M2" t="s">
+      <c r="K2" s="1">
+        <v>45581</v>
+      </c>
+      <c r="L2" s="9">
+        <f>G2+G3+G5+G6+10000</f>
+        <v>130960</v>
+      </c>
+      <c r="N2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" t="s">
         <v>15</v>
       </c>
-      <c r="O2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17">
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="1">
         <v>45581</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3">
         <v>900</v>
@@ -704,28 +722,35 @@
         <f>G3*VLOOKUP(A3,Precios!$A$3:$AA$601,27)</f>
         <v>54259920</v>
       </c>
-      <c r="M3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q3" t="s">
+      <c r="K3" s="1">
+        <v>45611</v>
+      </c>
+      <c r="L3" s="9">
+        <f>G11+G13+G15</f>
+        <v>97640</v>
+      </c>
+      <c r="N3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="P3" t="s">
+        <v>14</v>
+      </c>
+      <c r="R3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" hidden="1">
       <c r="A4" s="1">
         <v>45585</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4">
         <v>400</v>
@@ -745,22 +770,22 @@
         <f>G4*VLOOKUP(A4,Precios!$A$3:$AA$601,27)</f>
         <v>24157680</v>
       </c>
-      <c r="M4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="N4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="1">
-        <v>45613</v>
+        <v>45582</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5">
         <v>100</v>
@@ -774,25 +799,31 @@
       </c>
       <c r="H5" s="8">
         <f>F5*VLOOKUP(A5,Precios!$A$3:$AA$601,27)</f>
-        <v>58250</v>
+        <v>57250</v>
       </c>
       <c r="I5" s="8">
         <f>G5*VLOOKUP(A5,Precios!$A$3:$AA$601,27)</f>
-        <v>5825000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
+        <v>5725000</v>
+      </c>
+      <c r="K5" s="1">
+        <v>46006</v>
+      </c>
+      <c r="L5">
+        <v>-5000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="1">
         <v>45583</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6">
         <v>100</v>
@@ -812,19 +843,26 @@
         <f>G6*VLOOKUP(A6,Precios!$A$3:$AA$601,27)</f>
         <v>6039420</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="K6" s="1">
+        <v>45809</v>
+      </c>
+      <c r="L6" s="9">
+        <f>G19+G20+G22+G24+10000</f>
+        <v>101120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" hidden="1">
       <c r="A7" s="1">
         <v>45584</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7">
         <v>600</v>
@@ -845,18 +883,18 @@
         <v>36236520</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:18" hidden="1">
       <c r="A8" s="1">
         <v>45665</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8" s="9">
         <v>8000</v>
@@ -870,18 +908,18 @@
         <v>9584000</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:18" hidden="1">
       <c r="A9" s="1">
         <v>45665</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G9" s="9">
         <v>8000</v>
@@ -895,18 +933,18 @@
         <v>9584000</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:18" hidden="1">
       <c r="A10" s="1">
         <v>45665</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G10" s="9">
         <v>375</v>
@@ -920,18 +958,18 @@
         <v>449250</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:18">
       <c r="A11" s="1">
         <v>45665</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E11">
         <v>300</v>
@@ -951,19 +989,25 @@
         <f>G11*VLOOKUP(A11,Precios!$A$3:$AA$601,27)</f>
         <v>19407600</v>
       </c>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="K11" s="1">
+        <v>45915</v>
+      </c>
+      <c r="L11">
+        <v>-3000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" hidden="1">
       <c r="A12" s="1">
         <v>45667</v>
       </c>
       <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
         <v>15</v>
-      </c>
-      <c r="C12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" t="s">
-        <v>14</v>
       </c>
       <c r="E12">
         <v>1000</v>
@@ -984,18 +1028,18 @@
         <v>82200000</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:18">
       <c r="A13" s="1">
         <v>45669</v>
       </c>
       <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
         <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" t="s">
-        <v>11</v>
       </c>
       <c r="E13">
         <v>1000</v>
@@ -1016,18 +1060,18 @@
         <v>82200000</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:18" hidden="1">
       <c r="A14" s="1">
         <v>45669</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14">
         <v>1000</v>
@@ -1048,18 +1092,18 @@
         <v>82200000</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:18">
       <c r="A15" s="1">
         <v>45698</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E15">
         <v>200</v>
@@ -1080,18 +1124,18 @@
         <v>15799740</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:18" hidden="1">
       <c r="A16" s="1">
         <v>45846</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G16" s="9">
         <v>1600</v>
@@ -1105,18 +1149,18 @@
         <v>2107200</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" hidden="1">
       <c r="A17" s="1">
         <v>45846</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G17" s="9">
         <v>75</v>
@@ -1131,18 +1175,18 @@
       </c>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" hidden="1">
       <c r="A18" s="1">
         <v>45846</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G18" s="9">
         <f>1575/2</f>
@@ -1162,13 +1206,13 @@
         <v>45847</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E19">
         <v>300</v>
@@ -1194,13 +1238,13 @@
         <v>45848</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20">
         <v>600</v>
@@ -1221,18 +1265,18 @@
         <v>48001560</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" hidden="1">
       <c r="A21" s="1">
         <v>45879</v>
       </c>
       <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s">
         <v>15</v>
-      </c>
-      <c r="C21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" t="s">
-        <v>14</v>
       </c>
       <c r="E21">
         <v>800</v>
@@ -1258,13 +1302,13 @@
         <v>45910</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E22">
         <v>400</v>
@@ -1286,18 +1330,18 @@
       </c>
       <c r="S22" s="4"/>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" hidden="1">
       <c r="A23" s="1">
         <v>45912</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E23">
         <v>200</v>
@@ -1323,13 +1367,13 @@
         <v>45913</v>
       </c>
       <c r="B24" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E24">
         <v>300</v>
@@ -1350,18 +1394,18 @@
         <v>20445000</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" hidden="1">
       <c r="A25" s="1">
         <v>45914</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G25" s="9">
         <v>5000</v>
@@ -1412,12 +1456,18 @@
       <c r="A37" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G25" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G25" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Compra"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G17">
     <sortCondition ref="A2:A17"/>
   </sortState>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B11 B15:B37 M4" xr:uid="{D82FC90E-F4C1-4FEE-90A7-1E7B4FF2C652}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N4 B15:B37 B2:B11" xr:uid="{D82FC90E-F4C1-4FEE-90A7-1E7B4FF2C652}">
       <formula1>$M$1:$M$23</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1" xr:uid="{9837364A-ACA4-4040-937F-F0F8B099CD79}">
@@ -1453,87 +1503,87 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="W1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Y1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Z1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AA1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:28">
       <c r="A2" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2" s="11">
         <v>60.5</v>

--- a/operaciones.xlsx
+++ b/operaciones.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EE3E9BE-DA9A-48A0-B021-B68179F0871A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC03D041-284B-4F48-9CBA-3C6C528EB50C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -660,11 +660,11 @@
         <v>45580</v>
       </c>
       <c r="J2">
-        <v>300000</v>
+        <v>100000</v>
       </c>
       <c r="L2" s="13">
         <f>J2-K2</f>
-        <v>300000</v>
+        <v>100000</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="1"/>
@@ -714,7 +714,7 @@
       <c r="K3" s="8"/>
       <c r="L3" s="14">
         <f>L2+J3-K3</f>
-        <v>300000</v>
+        <v>100000</v>
       </c>
       <c r="M3" s="9"/>
       <c r="N3" s="1"/>
@@ -764,7 +764,7 @@
       <c r="K4" s="8"/>
       <c r="L4" s="14">
         <f>L3+J4-K4</f>
-        <v>300000</v>
+        <v>100000</v>
       </c>
       <c r="Q4" t="s">
         <v>23</v>
@@ -805,7 +805,7 @@
       <c r="K5" s="8"/>
       <c r="L5" s="14">
         <f t="shared" ref="L5:L26" si="0">L4+J5-K5</f>
-        <v>300000</v>
+        <v>100000</v>
       </c>
       <c r="N5" s="1"/>
     </row>
@@ -844,7 +844,7 @@
       <c r="K6" s="8"/>
       <c r="L6" s="14">
         <f t="shared" si="0"/>
-        <v>300000</v>
+        <v>100000</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="9"/>
@@ -884,7 +884,7 @@
       <c r="K7" s="8"/>
       <c r="L7" s="14">
         <f t="shared" si="0"/>
-        <v>300000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -922,7 +922,7 @@
       <c r="K8" s="8"/>
       <c r="L8" s="14">
         <f t="shared" si="0"/>
-        <v>300000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -953,7 +953,7 @@
       <c r="K9" s="8"/>
       <c r="L9" s="14">
         <f t="shared" si="0"/>
-        <v>300000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -986,7 +986,7 @@
       </c>
       <c r="L10" s="14">
         <f t="shared" si="0"/>
-        <v>292000</v>
+        <v>92000</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -1017,7 +1017,7 @@
       <c r="K11" s="8"/>
       <c r="L11" s="14">
         <f t="shared" si="0"/>
-        <v>292000</v>
+        <v>92000</v>
       </c>
       <c r="N11" s="1"/>
     </row>
@@ -1056,7 +1056,7 @@
       <c r="K12" s="8"/>
       <c r="L12" s="14">
         <f t="shared" si="0"/>
-        <v>292000</v>
+        <v>92000</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -1094,7 +1094,7 @@
       <c r="K13" s="8"/>
       <c r="L13" s="14">
         <f t="shared" si="0"/>
-        <v>292000</v>
+        <v>92000</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -1132,7 +1132,7 @@
       <c r="K14" s="8"/>
       <c r="L14" s="14">
         <f t="shared" si="0"/>
-        <v>292000</v>
+        <v>92000</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -1170,7 +1170,7 @@
       <c r="K15" s="8"/>
       <c r="L15" s="14">
         <f t="shared" si="0"/>
-        <v>292000</v>
+        <v>92000</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -1208,7 +1208,7 @@
       <c r="K16" s="8"/>
       <c r="L16" s="14">
         <f t="shared" si="0"/>
-        <v>292000</v>
+        <v>92000</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="L17" s="14">
         <f t="shared" si="0"/>
-        <v>290400</v>
+        <v>90400</v>
       </c>
       <c r="M17" s="3"/>
     </row>
@@ -1273,7 +1273,7 @@
       <c r="K18" s="8"/>
       <c r="L18" s="14">
         <f t="shared" si="0"/>
-        <v>290400</v>
+        <v>90400</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1305,7 +1305,7 @@
       <c r="K19" s="8"/>
       <c r="L19" s="14">
         <f t="shared" si="0"/>
-        <v>290400</v>
+        <v>90400</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -1343,7 +1343,7 @@
       <c r="K20" s="8"/>
       <c r="L20" s="14">
         <f t="shared" si="0"/>
-        <v>290400</v>
+        <v>90400</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -1381,7 +1381,7 @@
       <c r="K21" s="8"/>
       <c r="L21" s="14">
         <f t="shared" si="0"/>
-        <v>290400</v>
+        <v>90400</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -1419,7 +1419,7 @@
       <c r="K22" s="8"/>
       <c r="L22" s="14">
         <f t="shared" si="0"/>
-        <v>290400</v>
+        <v>90400</v>
       </c>
       <c r="V22" s="4"/>
     </row>
@@ -1458,7 +1458,7 @@
       <c r="K23" s="8"/>
       <c r="L23" s="14">
         <f t="shared" si="0"/>
-        <v>290400</v>
+        <v>90400</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -1496,7 +1496,7 @@
       <c r="K24" s="8"/>
       <c r="L24" s="14">
         <f t="shared" si="0"/>
-        <v>290400</v>
+        <v>90400</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -1534,7 +1534,7 @@
       <c r="K25" s="8"/>
       <c r="L25" s="14">
         <f t="shared" si="0"/>
-        <v>290400</v>
+        <v>90400</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -1565,7 +1565,7 @@
       <c r="K26" s="8"/>
       <c r="L26" s="14">
         <f t="shared" si="0"/>
-        <v>290400</v>
+        <v>90400</v>
       </c>
     </row>
     <row r="27" spans="1:22">

--- a/operaciones.xlsx
+++ b/operaciones.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC03D041-284B-4F48-9CBA-3C6C528EB50C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5FD161A-5D53-4A14-8D01-D6872F72D356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -660,11 +660,11 @@
         <v>45580</v>
       </c>
       <c r="J2">
-        <v>100000</v>
+        <v>70000</v>
       </c>
       <c r="L2" s="13">
         <f>J2-K2</f>
-        <v>100000</v>
+        <v>70000</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="1"/>
@@ -714,7 +714,7 @@
       <c r="K3" s="8"/>
       <c r="L3" s="14">
         <f>L2+J3-K3</f>
-        <v>100000</v>
+        <v>70000</v>
       </c>
       <c r="M3" s="9"/>
       <c r="N3" s="1"/>
@@ -764,7 +764,7 @@
       <c r="K4" s="8"/>
       <c r="L4" s="14">
         <f>L3+J4-K4</f>
-        <v>100000</v>
+        <v>70000</v>
       </c>
       <c r="Q4" t="s">
         <v>23</v>
@@ -805,7 +805,7 @@
       <c r="K5" s="8"/>
       <c r="L5" s="14">
         <f t="shared" ref="L5:L26" si="0">L4+J5-K5</f>
-        <v>100000</v>
+        <v>70000</v>
       </c>
       <c r="N5" s="1"/>
     </row>
@@ -844,7 +844,7 @@
       <c r="K6" s="8"/>
       <c r="L6" s="14">
         <f t="shared" si="0"/>
-        <v>100000</v>
+        <v>70000</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="9"/>
@@ -884,7 +884,7 @@
       <c r="K7" s="8"/>
       <c r="L7" s="14">
         <f t="shared" si="0"/>
-        <v>100000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -922,7 +922,7 @@
       <c r="K8" s="8"/>
       <c r="L8" s="14">
         <f t="shared" si="0"/>
-        <v>100000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -953,7 +953,7 @@
       <c r="K9" s="8"/>
       <c r="L9" s="14">
         <f t="shared" si="0"/>
-        <v>100000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -986,7 +986,7 @@
       </c>
       <c r="L10" s="14">
         <f t="shared" si="0"/>
-        <v>92000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -1017,7 +1017,7 @@
       <c r="K11" s="8"/>
       <c r="L11" s="14">
         <f t="shared" si="0"/>
-        <v>92000</v>
+        <v>62000</v>
       </c>
       <c r="N11" s="1"/>
     </row>
@@ -1056,7 +1056,7 @@
       <c r="K12" s="8"/>
       <c r="L12" s="14">
         <f t="shared" si="0"/>
-        <v>92000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -1094,7 +1094,7 @@
       <c r="K13" s="8"/>
       <c r="L13" s="14">
         <f t="shared" si="0"/>
-        <v>92000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -1132,7 +1132,7 @@
       <c r="K14" s="8"/>
       <c r="L14" s="14">
         <f t="shared" si="0"/>
-        <v>92000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -1170,7 +1170,7 @@
       <c r="K15" s="8"/>
       <c r="L15" s="14">
         <f t="shared" si="0"/>
-        <v>92000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -1208,7 +1208,7 @@
       <c r="K16" s="8"/>
       <c r="L16" s="14">
         <f t="shared" si="0"/>
-        <v>92000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="L17" s="14">
         <f t="shared" si="0"/>
-        <v>90400</v>
+        <v>60400</v>
       </c>
       <c r="M17" s="3"/>
     </row>
@@ -1273,7 +1273,7 @@
       <c r="K18" s="8"/>
       <c r="L18" s="14">
         <f t="shared" si="0"/>
-        <v>90400</v>
+        <v>60400</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1305,7 +1305,7 @@
       <c r="K19" s="8"/>
       <c r="L19" s="14">
         <f t="shared" si="0"/>
-        <v>90400</v>
+        <v>60400</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -1343,7 +1343,7 @@
       <c r="K20" s="8"/>
       <c r="L20" s="14">
         <f t="shared" si="0"/>
-        <v>90400</v>
+        <v>60400</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -1381,7 +1381,7 @@
       <c r="K21" s="8"/>
       <c r="L21" s="14">
         <f t="shared" si="0"/>
-        <v>90400</v>
+        <v>60400</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -1419,7 +1419,7 @@
       <c r="K22" s="8"/>
       <c r="L22" s="14">
         <f t="shared" si="0"/>
-        <v>90400</v>
+        <v>60400</v>
       </c>
       <c r="V22" s="4"/>
     </row>
@@ -1458,7 +1458,7 @@
       <c r="K23" s="8"/>
       <c r="L23" s="14">
         <f t="shared" si="0"/>
-        <v>90400</v>
+        <v>60400</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -1496,7 +1496,7 @@
       <c r="K24" s="8"/>
       <c r="L24" s="14">
         <f t="shared" si="0"/>
-        <v>90400</v>
+        <v>60400</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -1534,7 +1534,7 @@
       <c r="K25" s="8"/>
       <c r="L25" s="14">
         <f t="shared" si="0"/>
-        <v>90400</v>
+        <v>60400</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -1565,7 +1565,7 @@
       <c r="K26" s="8"/>
       <c r="L26" s="14">
         <f t="shared" si="0"/>
-        <v>90400</v>
+        <v>60400</v>
       </c>
     </row>
     <row r="27" spans="1:22">

--- a/operaciones.xlsx
+++ b/operaciones.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5FD161A-5D53-4A14-8D01-D6872F72D356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DCDC840-CC34-48A2-A0C4-AD51C31C32F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -950,10 +950,12 @@
         <v>9584000</v>
       </c>
       <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
+      <c r="K9" s="8">
+        <v>8000</v>
+      </c>
       <c r="L9" s="14">
         <f t="shared" si="0"/>
-        <v>70000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -986,7 +988,7 @@
       </c>
       <c r="L10" s="14">
         <f t="shared" si="0"/>
-        <v>62000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -1017,7 +1019,7 @@
       <c r="K11" s="8"/>
       <c r="L11" s="14">
         <f t="shared" si="0"/>
-        <v>62000</v>
+        <v>54000</v>
       </c>
       <c r="N11" s="1"/>
     </row>
@@ -1056,7 +1058,7 @@
       <c r="K12" s="8"/>
       <c r="L12" s="14">
         <f t="shared" si="0"/>
-        <v>62000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -1094,7 +1096,7 @@
       <c r="K13" s="8"/>
       <c r="L13" s="14">
         <f t="shared" si="0"/>
-        <v>62000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -1132,7 +1134,7 @@
       <c r="K14" s="8"/>
       <c r="L14" s="14">
         <f t="shared" si="0"/>
-        <v>62000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -1167,10 +1169,12 @@
         <v>82200000</v>
       </c>
       <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
+      <c r="K15" s="8">
+        <v>30000</v>
+      </c>
       <c r="L15" s="14">
         <f t="shared" si="0"/>
-        <v>62000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -1208,7 +1212,7 @@
       <c r="K16" s="8"/>
       <c r="L16" s="14">
         <f t="shared" si="0"/>
-        <v>62000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -1241,7 +1245,7 @@
       </c>
       <c r="L17" s="14">
         <f t="shared" si="0"/>
-        <v>60400</v>
+        <v>22400</v>
       </c>
       <c r="M17" s="3"/>
     </row>
@@ -1273,7 +1277,7 @@
       <c r="K18" s="8"/>
       <c r="L18" s="14">
         <f t="shared" si="0"/>
-        <v>60400</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1305,7 +1309,7 @@
       <c r="K19" s="8"/>
       <c r="L19" s="14">
         <f t="shared" si="0"/>
-        <v>60400</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -1343,7 +1347,7 @@
       <c r="K20" s="8"/>
       <c r="L20" s="14">
         <f t="shared" si="0"/>
-        <v>60400</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -1381,7 +1385,7 @@
       <c r="K21" s="8"/>
       <c r="L21" s="14">
         <f t="shared" si="0"/>
-        <v>60400</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -1419,7 +1423,7 @@
       <c r="K22" s="8"/>
       <c r="L22" s="14">
         <f t="shared" si="0"/>
-        <v>60400</v>
+        <v>22400</v>
       </c>
       <c r="V22" s="4"/>
     </row>
@@ -1458,7 +1462,7 @@
       <c r="K23" s="8"/>
       <c r="L23" s="14">
         <f t="shared" si="0"/>
-        <v>60400</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -1496,7 +1500,7 @@
       <c r="K24" s="8"/>
       <c r="L24" s="14">
         <f t="shared" si="0"/>
-        <v>60400</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -1534,7 +1538,7 @@
       <c r="K25" s="8"/>
       <c r="L25" s="14">
         <f t="shared" si="0"/>
-        <v>60400</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -1565,7 +1569,7 @@
       <c r="K26" s="8"/>
       <c r="L26" s="14">
         <f t="shared" si="0"/>
-        <v>60400</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="27" spans="1:22">

--- a/operaciones.xlsx
+++ b/operaciones.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DCDC840-CC34-48A2-A0C4-AD51C31C32F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D155519-C603-459F-858D-351BB0563DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1169,12 +1169,10 @@
         <v>82200000</v>
       </c>
       <c r="J15" s="8"/>
-      <c r="K15" s="8">
-        <v>30000</v>
-      </c>
+      <c r="K15" s="8"/>
       <c r="L15" s="14">
         <f t="shared" si="0"/>
-        <v>24000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -1212,7 +1210,7 @@
       <c r="K16" s="8"/>
       <c r="L16" s="14">
         <f t="shared" si="0"/>
-        <v>24000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -1245,7 +1243,7 @@
       </c>
       <c r="L17" s="14">
         <f t="shared" si="0"/>
-        <v>22400</v>
+        <v>52400</v>
       </c>
       <c r="M17" s="3"/>
     </row>
@@ -1277,7 +1275,7 @@
       <c r="K18" s="8"/>
       <c r="L18" s="14">
         <f t="shared" si="0"/>
-        <v>22400</v>
+        <v>52400</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1309,7 +1307,7 @@
       <c r="K19" s="8"/>
       <c r="L19" s="14">
         <f t="shared" si="0"/>
-        <v>22400</v>
+        <v>52400</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -1347,7 +1345,7 @@
       <c r="K20" s="8"/>
       <c r="L20" s="14">
         <f t="shared" si="0"/>
-        <v>22400</v>
+        <v>52400</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -1385,7 +1383,7 @@
       <c r="K21" s="8"/>
       <c r="L21" s="14">
         <f t="shared" si="0"/>
-        <v>22400</v>
+        <v>52400</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -1423,7 +1421,7 @@
       <c r="K22" s="8"/>
       <c r="L22" s="14">
         <f t="shared" si="0"/>
-        <v>22400</v>
+        <v>52400</v>
       </c>
       <c r="V22" s="4"/>
     </row>
@@ -1462,7 +1460,7 @@
       <c r="K23" s="8"/>
       <c r="L23" s="14">
         <f t="shared" si="0"/>
-        <v>22400</v>
+        <v>52400</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -1497,7 +1495,9 @@
         <v>14720400</v>
       </c>
       <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
+      <c r="K24" s="8">
+        <v>30000</v>
+      </c>
       <c r="L24" s="14">
         <f t="shared" si="0"/>
         <v>22400</v>

--- a/operaciones.xlsx
+++ b/operaciones.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30002"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D155519-C603-459F-858D-351BB0563DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{14CFD141-0BAB-45BF-9082-B2E571B989C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12,7 +12,7 @@
     <sheet name="Precios" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Operaciones!$A$1:$G$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Operaciones!$A$1:$G$25</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -185,8 +185,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="[$-C0A]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -231,7 +232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -253,6 +254,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -587,10 +589,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V37"/>
+  <dimension ref="A1:W27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" style="15" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" customWidth="1"/>
     <col min="3" max="3" width="14.28515625" customWidth="1"/>
     <col min="4" max="4" width="14.140625" customWidth="1"/>
@@ -598,18 +600,18 @@
     <col min="6" max="6" width="13.85546875" customWidth="1"/>
     <col min="7" max="7" width="15.5703125" style="9" customWidth="1"/>
     <col min="8" max="8" width="12.140625" style="9" customWidth="1"/>
-    <col min="9" max="12" width="14.140625" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" customWidth="1"/>
-    <col min="16" max="16" width="13.28515625" customWidth="1"/>
-    <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.28515625" customWidth="1"/>
-    <col min="22" max="22" width="12.85546875" customWidth="1"/>
+    <col min="9" max="13" width="14.140625" customWidth="1"/>
+    <col min="15" max="15" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" customWidth="1"/>
+    <col min="17" max="17" width="13.28515625" customWidth="1"/>
+    <col min="18" max="18" width="11" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.28515625" customWidth="1"/>
+    <col min="23" max="23" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
-      <c r="A1" t="s">
+    <row r="1" spans="1:22">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -636,51 +638,51 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>12</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>13</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="18" customHeight="1">
-      <c r="A2" s="1">
+    <row r="2" spans="1:22" ht="18" customHeight="1">
+      <c r="A2" s="15">
         <v>45580</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>70000</v>
       </c>
-      <c r="L2" s="13">
-        <f>J2-K2</f>
+      <c r="M2" s="13">
+        <f>K2-L2</f>
         <v>70000</v>
       </c>
-      <c r="M2" s="9"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="9"/>
-      <c r="Q2" t="s">
+      <c r="N2" s="9"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="9"/>
+      <c r="R2" t="s">
         <v>15</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>16</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="1">
+    <row r="3" spans="1:22">
+      <c r="A3" s="15">
         <v>45581</v>
       </c>
       <c r="B3" t="s">
@@ -712,25 +714,26 @@
       </c>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
-      <c r="L3" s="14">
-        <f>L2+J3-K3</f>
+      <c r="L3" s="8"/>
+      <c r="M3" s="14">
+        <f>M2+K3-L3</f>
         <v>70000</v>
       </c>
-      <c r="M3" s="9"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="9"/>
-      <c r="Q3" t="s">
+      <c r="N3" s="9"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="9"/>
+      <c r="R3" t="s">
         <v>20</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>19</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="1">
+    <row r="4" spans="1:22">
+      <c r="A4" s="15">
         <v>45581</v>
       </c>
       <c r="B4" t="s">
@@ -762,16 +765,17 @@
       </c>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
-      <c r="L4" s="14">
-        <f>L3+J4-K4</f>
+      <c r="L4" s="8"/>
+      <c r="M4" s="14">
+        <f>M3+K4-L4</f>
         <v>70000</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="1">
+    <row r="5" spans="1:22">
+      <c r="A5" s="15">
         <v>45585</v>
       </c>
       <c r="B5" t="s">
@@ -803,14 +807,15 @@
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
-      <c r="L5" s="14">
-        <f t="shared" ref="L5:L26" si="0">L4+J5-K5</f>
+      <c r="L5" s="8"/>
+      <c r="M5" s="14">
+        <f t="shared" ref="M5:M27" si="0">M4+K5-L5</f>
         <v>70000</v>
       </c>
-      <c r="N5" s="1"/>
-    </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="1">
+      <c r="O5" s="1"/>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="A6" s="15">
         <v>45582</v>
       </c>
       <c r="B6" t="s">
@@ -823,14 +828,14 @@
         <v>24</v>
       </c>
       <c r="E6">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F6">
         <v>50</v>
       </c>
       <c r="G6" s="9">
         <f>+F6*E6</f>
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="H6" s="8">
         <f>F6*VLOOKUP(A6,Precios!$A$3:$AA$601,27)</f>
@@ -838,19 +843,20 @@
       </c>
       <c r="I6" s="8">
         <f>G6*VLOOKUP(A6,Precios!$A$3:$AA$601,27)</f>
-        <v>5725000</v>
+        <v>11450000</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
-      <c r="L6" s="14">
+      <c r="L6" s="8"/>
+      <c r="M6" s="14">
         <f t="shared" si="0"/>
         <v>70000</v>
       </c>
-      <c r="N6" s="1"/>
-      <c r="O6" s="9"/>
-    </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="1">
+      <c r="O6" s="1"/>
+      <c r="P6" s="9"/>
+    </row>
+    <row r="7" spans="1:22">
+      <c r="A7" s="15">
         <v>45583</v>
       </c>
       <c r="B7" t="s">
@@ -882,13 +888,14 @@
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
-      <c r="L7" s="14">
+      <c r="L7" s="8"/>
+      <c r="M7" s="14">
         <f t="shared" si="0"/>
         <v>70000</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="1">
+    <row r="8" spans="1:22">
+      <c r="A8" s="15">
         <v>45584</v>
       </c>
       <c r="B8" t="s">
@@ -920,13 +927,14 @@
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
-      <c r="L8" s="14">
+      <c r="L8" s="8"/>
+      <c r="M8" s="14">
         <f t="shared" si="0"/>
         <v>70000</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="1">
+    <row r="9" spans="1:22">
+      <c r="A9" s="15">
         <v>45665</v>
       </c>
       <c r="B9" t="s">
@@ -950,16 +958,17 @@
         <v>9584000</v>
       </c>
       <c r="J9" s="8"/>
-      <c r="K9" s="8">
+      <c r="K9" s="8"/>
+      <c r="L9" s="8">
         <v>8000</v>
       </c>
-      <c r="L9" s="14">
+      <c r="M9" s="14">
         <f t="shared" si="0"/>
         <v>62000</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
-      <c r="A10" s="1">
+    <row r="10" spans="1:22">
+      <c r="A10" s="15">
         <v>45665</v>
       </c>
       <c r="B10" t="s">
@@ -983,16 +992,17 @@
         <v>9584000</v>
       </c>
       <c r="J10" s="8"/>
-      <c r="K10" s="8">
+      <c r="K10" s="8"/>
+      <c r="L10" s="8">
         <v>8000</v>
       </c>
-      <c r="L10" s="14">
+      <c r="M10" s="14">
         <f t="shared" si="0"/>
         <v>54000</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
-      <c r="A11" s="1">
+    <row r="11" spans="1:22">
+      <c r="A11" s="15">
         <v>45665</v>
       </c>
       <c r="B11" t="s">
@@ -1017,14 +1027,15 @@
       </c>
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
-      <c r="L11" s="14">
+      <c r="L11" s="8"/>
+      <c r="M11" s="14">
         <f t="shared" si="0"/>
         <v>54000</v>
       </c>
-      <c r="N11" s="1"/>
-    </row>
-    <row r="12" spans="1:21">
-      <c r="A12" s="1">
+      <c r="O11" s="1"/>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="A12" s="15">
         <v>45665</v>
       </c>
       <c r="B12" t="s">
@@ -1056,13 +1067,14 @@
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
-      <c r="L12" s="14">
+      <c r="L12" s="8"/>
+      <c r="M12" s="14">
         <f t="shared" si="0"/>
         <v>54000</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="1">
+    <row r="13" spans="1:22">
+      <c r="A13" s="15">
         <v>45667</v>
       </c>
       <c r="B13" t="s">
@@ -1094,13 +1106,14 @@
       </c>
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
-      <c r="L13" s="14">
+      <c r="L13" s="8"/>
+      <c r="M13" s="14">
         <f t="shared" si="0"/>
         <v>54000</v>
       </c>
     </row>
-    <row r="14" spans="1:21">
-      <c r="A14" s="1">
+    <row r="14" spans="1:22">
+      <c r="A14" s="15">
         <v>45669</v>
       </c>
       <c r="B14" t="s">
@@ -1132,13 +1145,14 @@
       </c>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
-      <c r="L14" s="14">
+      <c r="L14" s="8"/>
+      <c r="M14" s="14">
         <f t="shared" si="0"/>
         <v>54000</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="1">
+    <row r="15" spans="1:22">
+      <c r="A15" s="15">
         <v>45669</v>
       </c>
       <c r="B15" t="s">
@@ -1170,13 +1184,14 @@
       </c>
       <c r="J15" s="8"/>
       <c r="K15" s="8"/>
-      <c r="L15" s="14">
+      <c r="L15" s="8"/>
+      <c r="M15" s="14">
         <f t="shared" si="0"/>
         <v>54000</v>
       </c>
     </row>
-    <row r="16" spans="1:21">
-      <c r="A16" s="1">
+    <row r="16" spans="1:22">
+      <c r="A16" s="15">
         <v>45698</v>
       </c>
       <c r="B16" t="s">
@@ -1208,13 +1223,14 @@
       </c>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
-      <c r="L16" s="14">
+      <c r="L16" s="8"/>
+      <c r="M16" s="14">
         <f t="shared" si="0"/>
         <v>54000</v>
       </c>
     </row>
-    <row r="17" spans="1:22">
-      <c r="A17" s="1">
+    <row r="17" spans="1:23">
+      <c r="A17" s="15">
         <v>45846</v>
       </c>
       <c r="B17" t="s">
@@ -1238,17 +1254,18 @@
         <v>2107200</v>
       </c>
       <c r="J17" s="8"/>
-      <c r="K17" s="8">
+      <c r="K17" s="8"/>
+      <c r="L17" s="8">
         <v>1600</v>
       </c>
-      <c r="L17" s="14">
+      <c r="M17" s="14">
         <f t="shared" si="0"/>
         <v>52400</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="1:22">
-      <c r="A18" s="1">
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="1:23">
+      <c r="A18" s="15">
         <v>45846</v>
       </c>
       <c r="B18" t="s">
@@ -1273,13 +1290,14 @@
       </c>
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
-      <c r="L18" s="14">
+      <c r="L18" s="8"/>
+      <c r="M18" s="14">
         <f t="shared" si="0"/>
         <v>52400</v>
       </c>
     </row>
-    <row r="19" spans="1:22">
-      <c r="A19" s="1">
+    <row r="19" spans="1:23">
+      <c r="A19" s="15">
         <v>45846</v>
       </c>
       <c r="B19" t="s">
@@ -1305,13 +1323,14 @@
       </c>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
-      <c r="L19" s="14">
+      <c r="L19" s="8"/>
+      <c r="M19" s="14">
         <f t="shared" si="0"/>
         <v>52400</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
-      <c r="A20" s="1">
+    <row r="20" spans="1:23">
+      <c r="A20" s="15">
         <v>45847</v>
       </c>
       <c r="B20" t="s">
@@ -1343,13 +1362,14 @@
       </c>
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
-      <c r="L20" s="14">
+      <c r="L20" s="8"/>
+      <c r="M20" s="14">
         <f t="shared" si="0"/>
         <v>52400</v>
       </c>
     </row>
-    <row r="21" spans="1:22">
-      <c r="A21" s="1">
+    <row r="21" spans="1:23">
+      <c r="A21" s="15">
         <v>45848</v>
       </c>
       <c r="B21" t="s">
@@ -1381,94 +1401,74 @@
       </c>
       <c r="J21" s="8"/>
       <c r="K21" s="8"/>
-      <c r="L21" s="14">
-        <f t="shared" si="0"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="14">
+        <f>M20+K21-L21</f>
         <v>52400</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
-      <c r="A22" s="1">
-        <v>45879</v>
-      </c>
-      <c r="B22" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22">
-        <v>800</v>
-      </c>
-      <c r="F22">
-        <v>58</v>
-      </c>
-      <c r="G22" s="9">
-        <f>+F22*E22</f>
-        <v>46400</v>
-      </c>
-      <c r="H22" s="8">
-        <f>F22*VLOOKUP(A22,Precios!$A$3:$AA$601,27)</f>
-        <v>77662</v>
-      </c>
-      <c r="I22" s="8">
-        <f>G22*VLOOKUP(A22,Precios!$A$3:$AA$601,27)</f>
-        <v>62129600</v>
-      </c>
+    <row r="22" spans="1:23">
+      <c r="A22" s="15">
+        <v>45863</v>
+      </c>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
-      <c r="L22" s="14">
-        <f t="shared" si="0"/>
-        <v>52400</v>
-      </c>
-      <c r="V22" s="4"/>
-    </row>
-    <row r="23" spans="1:22">
-      <c r="A23" s="1">
-        <v>45910</v>
+      <c r="L22" s="8">
+        <v>10000</v>
+      </c>
+      <c r="M22" s="14">
+        <f>M21+K22-L22</f>
+        <v>42400</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23">
+      <c r="A23" s="15">
+        <v>45879</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C23" t="s">
         <v>19</v>
       </c>
       <c r="D23" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E23">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="F23">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G23" s="9">
         <f>+F23*E23</f>
-        <v>22000</v>
+        <v>46400</v>
       </c>
       <c r="H23" s="8">
         <f>F23*VLOOKUP(A23,Precios!$A$3:$AA$601,27)</f>
-        <v>74855</v>
+        <v>77662</v>
       </c>
       <c r="I23" s="8">
         <f>G23*VLOOKUP(A23,Precios!$A$3:$AA$601,27)</f>
-        <v>29942000</v>
+        <v>62129600</v>
       </c>
       <c r="J23" s="8"/>
       <c r="K23" s="8"/>
-      <c r="L23" s="14">
-        <f t="shared" si="0"/>
-        <v>52400</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
-      <c r="A24" s="1">
-        <v>45912</v>
+      <c r="L23" s="8"/>
+      <c r="M23" s="14">
+        <f t="shared" ref="M23:M27" si="1">M22+K23-L23</f>
+        <v>42400</v>
+      </c>
+      <c r="W23" s="4"/>
+    </row>
+    <row r="24" spans="1:23">
+      <c r="A24" s="15">
+        <v>45910</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s">
         <v>19</v>
@@ -1477,76 +1477,78 @@
         <v>21</v>
       </c>
       <c r="E24">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F24">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G24" s="9">
         <f>+F24*E24</f>
-        <v>10800</v>
+        <v>22000</v>
       </c>
       <c r="H24" s="8">
         <f>F24*VLOOKUP(A24,Precios!$A$3:$AA$601,27)</f>
-        <v>73602</v>
+        <v>74855</v>
       </c>
       <c r="I24" s="8">
         <f>G24*VLOOKUP(A24,Precios!$A$3:$AA$601,27)</f>
-        <v>14720400</v>
+        <v>29942000</v>
       </c>
       <c r="J24" s="8"/>
-      <c r="K24" s="8">
-        <v>30000</v>
-      </c>
-      <c r="L24" s="14">
-        <f t="shared" si="0"/>
-        <v>22400</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22">
-      <c r="A25" s="1">
-        <v>45913</v>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="14">
+        <f t="shared" si="1"/>
+        <v>42400</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23">
+      <c r="A25" s="15">
+        <v>45912</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C25" t="s">
         <v>19</v>
       </c>
       <c r="D25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E25">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F25">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G25" s="9">
         <f>+F25*E25</f>
-        <v>15000</v>
+        <v>10800</v>
       </c>
       <c r="H25" s="8">
         <f>F25*VLOOKUP(A25,Precios!$A$3:$AA$601,27)</f>
-        <v>68150</v>
+        <v>73602</v>
       </c>
       <c r="I25" s="8">
         <f>G25*VLOOKUP(A25,Precios!$A$3:$AA$601,27)</f>
-        <v>20445000</v>
+        <v>14720400</v>
       </c>
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
-      <c r="L25" s="14">
-        <f t="shared" si="0"/>
-        <v>22400</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
-      <c r="A26" s="1">
-        <v>45914</v>
+      <c r="L25" s="8">
+        <v>5000</v>
+      </c>
+      <c r="M25" s="14">
+        <f t="shared" si="1"/>
+        <v>37400</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23">
+      <c r="A26" s="15">
+        <v>45913</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
         <v>19</v>
@@ -1554,77 +1556,84 @@
       <c r="D26" t="s">
         <v>22</v>
       </c>
+      <c r="E26">
+        <v>300</v>
+      </c>
+      <c r="F26">
+        <v>50</v>
+      </c>
       <c r="G26" s="9">
-        <v>5000</v>
+        <f>+F26*E26</f>
+        <v>15000</v>
       </c>
       <c r="H26" s="8">
         <f>F26*VLOOKUP(A26,Precios!$A$3:$AA$601,27)</f>
-        <v>0</v>
+        <v>68150</v>
       </c>
       <c r="I26" s="8">
         <f>G26*VLOOKUP(A26,Precios!$A$3:$AA$601,27)</f>
-        <v>6815000</v>
+        <v>20445000</v>
       </c>
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
-      <c r="L26" s="14">
-        <f t="shared" si="0"/>
-        <v>22400</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22">
-      <c r="A27" s="1"/>
-    </row>
-    <row r="28" spans="1:22">
-      <c r="A28" s="1"/>
-    </row>
-    <row r="29" spans="1:22">
-      <c r="A29" s="1"/>
-    </row>
-    <row r="30" spans="1:22">
-      <c r="A30" s="1"/>
-    </row>
-    <row r="31" spans="1:22">
-      <c r="A31" s="1"/>
-    </row>
-    <row r="32" spans="1:22">
-      <c r="A32" s="1"/>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1"/>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="1"/>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1"/>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1"/>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="1"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="14">
+        <f t="shared" si="1"/>
+        <v>37400</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23">
+      <c r="A27" s="15">
+        <v>45914</v>
+      </c>
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="9">
+        <v>5000</v>
+      </c>
+      <c r="H27" s="8">
+        <f>F27*VLOOKUP(A27,Precios!$A$3:$AA$601,27)</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="8">
+        <f>G27*VLOOKUP(A27,Precios!$A$3:$AA$601,27)</f>
+        <v>6815000</v>
+      </c>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="14">
+        <f t="shared" si="1"/>
+        <v>37400</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G25" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G27" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G18">
     <sortCondition ref="A3:A18"/>
   </sortState>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q4 B14 B3:B12 B16:B37" xr:uid="{D82FC90E-F4C1-4FEE-90A7-1E7B4FF2C652}">
-      <formula1>$P$1:$P$23</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1" xr:uid="{9837364A-ACA4-4040-937F-F0F8B099CD79}">
-      <formula1>$P$1:$P$17</formula1>
+      <formula1>$Q$1:$Q$17</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{5ACDAC43-0A2C-44ED-89F3-6CC7CBBC5473}">
-      <formula1>$R$1:$R$12</formula1>
+      <formula1>$S$1:$S$12</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R4 B14 B3:B12 B16:B38" xr:uid="{D82FC90E-F4C1-4FEE-90A7-1E7B4FF2C652}">
+      <formula1>$Q$1:$Q$24</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{072F3766-733D-4D00-B107-5AF1B31BCE79}">
-      <formula1>$T$1:$T$35</formula1>
+      <formula1>$U$1:$U$36</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D42" xr:uid="{ED8D13E1-2439-4B9C-AEC1-F990B45E5811}">
-      <formula1>$T$1:$T$57</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D43" xr:uid="{ED8D13E1-2439-4B9C-AEC1-F990B45E5811}">
+      <formula1>$U$1:$U$58</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/operaciones.xlsx
+++ b/operaciones.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30002"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{14CFD141-0BAB-45BF-9082-B2E571B989C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7855BA97-534F-4177-9D7C-0E6886B7C8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12,7 +12,7 @@
     <sheet name="Precios" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Operaciones!$A$1:$G$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Operaciones!$A$1:$G$27</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="49">
   <si>
     <t>Fecha</t>
   </si>
@@ -80,6 +80,9 @@
   </si>
   <si>
     <t>AL29</t>
+  </si>
+  <si>
+    <t>Retiro/Ingreso</t>
   </si>
   <si>
     <t>Venta</t>
@@ -212,18 +215,44 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -232,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -250,11 +279,21 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -589,10 +628,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W27"/>
+  <dimension ref="A1:W30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" style="23" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" customWidth="1"/>
     <col min="3" max="3" width="14.28515625" customWidth="1"/>
     <col min="4" max="4" width="14.140625" customWidth="1"/>
@@ -600,51 +639,55 @@
     <col min="6" max="6" width="13.85546875" customWidth="1"/>
     <col min="7" max="7" width="15.5703125" style="9" customWidth="1"/>
     <col min="8" max="8" width="12.140625" style="9" customWidth="1"/>
-    <col min="9" max="13" width="14.140625" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" customWidth="1"/>
+    <col min="10" max="10" width="6.42578125" style="16" customWidth="1"/>
+    <col min="11" max="12" width="14.140625" customWidth="1"/>
+    <col min="13" max="13" width="14.140625" style="21" customWidth="1"/>
     <col min="15" max="15" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.7109375" customWidth="1"/>
     <col min="17" max="17" width="13.28515625" customWidth="1"/>
-    <col min="18" max="18" width="11" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="13.28515625" customWidth="1"/>
     <col min="23" max="23" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="J1" s="15"/>
+      <c r="K1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="18" t="s">
         <v>11</v>
       </c>
       <c r="R1" t="s">
@@ -658,13 +701,16 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="18" customHeight="1">
-      <c r="A2" s="15">
+      <c r="A2" s="23">
         <v>45580</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
       </c>
       <c r="K2">
         <v>70000</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="19">
         <f>K2-L2</f>
         <v>70000</v>
       </c>
@@ -672,27 +718,27 @@
       <c r="O2" s="1"/>
       <c r="P2" s="9"/>
       <c r="R2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:22">
-      <c r="A3" s="15">
+      <c r="A3" s="23">
         <v>45581</v>
       </c>
       <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
         <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
       </c>
       <c r="E3">
         <v>1000</v>
@@ -712,10 +758,10 @@
         <f>G3*VLOOKUP(A3,Precios!$A$3:$AA$601,27)</f>
         <v>72369440</v>
       </c>
-      <c r="J3" s="8"/>
+      <c r="J3" s="17"/>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
-      <c r="M3" s="14">
+      <c r="M3" s="20">
         <f>M2+K3-L3</f>
         <v>70000</v>
       </c>
@@ -723,27 +769,27 @@
       <c r="O3" s="1"/>
       <c r="P3" s="9"/>
       <c r="R3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T3" t="s">
         <v>20</v>
       </c>
-      <c r="T3" t="s">
+      <c r="V3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" s="23">
+        <v>45581</v>
+      </c>
+      <c r="B4" t="s">
         <v>19</v>
       </c>
-      <c r="V3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
-      <c r="A4" s="15">
-        <v>45581</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4">
         <v>900</v>
@@ -763,29 +809,29 @@
         <f>G4*VLOOKUP(A4,Precios!$A$3:$AA$601,27)</f>
         <v>54259920</v>
       </c>
-      <c r="J4" s="8"/>
+      <c r="J4" s="17"/>
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="14">
+      <c r="M4" s="20">
         <f>M3+K4-L4</f>
         <v>70000</v>
       </c>
       <c r="R4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5" s="23">
+        <v>45585</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22">
-      <c r="A5" s="15">
-        <v>45585</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
       </c>
       <c r="E5">
         <v>400</v>
@@ -805,27 +851,30 @@
         <f>G5*VLOOKUP(A5,Precios!$A$3:$AA$601,27)</f>
         <v>24157680</v>
       </c>
-      <c r="J5" s="8"/>
+      <c r="J5" s="17"/>
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
-      <c r="M5" s="14">
-        <f t="shared" ref="M5:M27" si="0">M4+K5-L5</f>
+      <c r="M5" s="20">
+        <f t="shared" ref="M5:M22" si="0">M4+K5-L5</f>
         <v>70000</v>
       </c>
       <c r="O5" s="1"/>
+      <c r="R5" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="6" spans="1:22">
-      <c r="A6" s="15">
+      <c r="A6" s="23">
         <v>45582</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6">
         <v>200</v>
@@ -845,10 +894,10 @@
         <f>G6*VLOOKUP(A6,Precios!$A$3:$AA$601,27)</f>
         <v>11450000</v>
       </c>
-      <c r="J6" s="8"/>
+      <c r="J6" s="17"/>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
-      <c r="M6" s="14">
+      <c r="M6" s="20">
         <f t="shared" si="0"/>
         <v>70000</v>
       </c>
@@ -856,17 +905,17 @@
       <c r="P6" s="9"/>
     </row>
     <row r="7" spans="1:22">
-      <c r="A7" s="15">
+      <c r="A7" s="23">
         <v>45583</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -886,26 +935,26 @@
         <f>G7*VLOOKUP(A7,Precios!$A$3:$AA$601,27)</f>
         <v>6039420</v>
       </c>
-      <c r="J7" s="8"/>
+      <c r="J7" s="17"/>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
-      <c r="M7" s="14">
+      <c r="M7" s="20">
         <f t="shared" si="0"/>
         <v>70000</v>
       </c>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" s="15">
+      <c r="A8" s="23">
         <v>45584</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8">
         <v>600</v>
@@ -925,26 +974,26 @@
         <f>G8*VLOOKUP(A8,Precios!$A$3:$AA$601,27)</f>
         <v>36236520</v>
       </c>
-      <c r="J8" s="8"/>
+      <c r="J8" s="17"/>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
-      <c r="M8" s="14">
+      <c r="M8" s="20">
         <f t="shared" si="0"/>
         <v>70000</v>
       </c>
     </row>
     <row r="9" spans="1:22">
-      <c r="A9" s="15">
+      <c r="A9" s="23">
         <v>45665</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G9" s="9">
         <v>8000</v>
@@ -957,28 +1006,26 @@
         <f>G9*VLOOKUP(A9,Precios!$A$3:$AA$601,27)</f>
         <v>9584000</v>
       </c>
-      <c r="J9" s="8"/>
+      <c r="J9" s="17"/>
       <c r="K9" s="8"/>
-      <c r="L9" s="8">
-        <v>8000</v>
-      </c>
-      <c r="M9" s="14">
+      <c r="L9" s="8"/>
+      <c r="M9" s="20">
         <f t="shared" si="0"/>
-        <v>62000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="10" spans="1:22">
-      <c r="A10" s="15">
+      <c r="A10" s="23">
         <v>45665</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G10" s="9">
         <v>8000</v>
@@ -991,139 +1038,114 @@
         <f>G10*VLOOKUP(A10,Precios!$A$3:$AA$601,27)</f>
         <v>9584000</v>
       </c>
-      <c r="J10" s="8"/>
+      <c r="J10" s="17"/>
       <c r="K10" s="8"/>
-      <c r="L10" s="8">
-        <v>8000</v>
-      </c>
-      <c r="M10" s="14">
+      <c r="L10" s="8"/>
+      <c r="M10" s="20">
         <f t="shared" si="0"/>
-        <v>54000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="11" spans="1:22">
-      <c r="A11" s="15">
+      <c r="A11" s="23">
         <v>45665</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="9">
+        <v>15</v>
+      </c>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8">
+        <v>16000</v>
+      </c>
+      <c r="M11" s="20"/>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="A12" s="23">
+        <v>45665</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="9">
         <v>375</v>
-      </c>
-      <c r="H11" s="8">
-        <f>F11*VLOOKUP(A11,Precios!$A$3:$AA$601,27)</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="8">
-        <f>G11*VLOOKUP(A11,Precios!$A$3:$AA$601,27)</f>
-        <v>449250</v>
-      </c>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="14">
-        <f t="shared" si="0"/>
-        <v>54000</v>
-      </c>
-      <c r="O11" s="1"/>
-    </row>
-    <row r="12" spans="1:22">
-      <c r="A12" s="15">
-        <v>45665</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12">
-        <v>300</v>
-      </c>
-      <c r="F12">
-        <v>54</v>
-      </c>
-      <c r="G12" s="9">
-        <f>E12*F12</f>
-        <v>16200</v>
       </c>
       <c r="H12" s="8">
         <f>F12*VLOOKUP(A12,Precios!$A$3:$AA$601,27)</f>
-        <v>64692</v>
+        <v>0</v>
       </c>
       <c r="I12" s="8">
         <f>G12*VLOOKUP(A12,Precios!$A$3:$AA$601,27)</f>
-        <v>19407600</v>
-      </c>
-      <c r="J12" s="8"/>
+        <v>449250</v>
+      </c>
+      <c r="J12" s="17"/>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
-      <c r="M12" s="14">
-        <f t="shared" si="0"/>
-        <v>54000</v>
-      </c>
+      <c r="M12" s="20">
+        <f>M10+K12-L12</f>
+        <v>70000</v>
+      </c>
+      <c r="O12" s="1"/>
     </row>
     <row r="13" spans="1:22">
-      <c r="A13" s="15">
-        <v>45667</v>
+      <c r="A13" s="23">
+        <v>45665</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E13">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="F13">
-        <v>68.5</v>
+        <v>54</v>
       </c>
       <c r="G13" s="9">
-        <f>+F13*E13</f>
-        <v>68500</v>
+        <f>E13*F13</f>
+        <v>16200</v>
       </c>
       <c r="H13" s="8">
         <f>F13*VLOOKUP(A13,Precios!$A$3:$AA$601,27)</f>
-        <v>82200</v>
+        <v>64692</v>
       </c>
       <c r="I13" s="8">
         <f>G13*VLOOKUP(A13,Precios!$A$3:$AA$601,27)</f>
-        <v>82200000</v>
-      </c>
-      <c r="J13" s="8"/>
+        <v>19407600</v>
+      </c>
+      <c r="J13" s="17"/>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
-      <c r="M13" s="14">
+      <c r="M13" s="20">
         <f t="shared" si="0"/>
-        <v>54000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="14" spans="1:22">
-      <c r="A14" s="15">
-        <v>45669</v>
+      <c r="A14" s="23">
+        <v>45667</v>
       </c>
       <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" t="s">
         <v>18</v>
-      </c>
-      <c r="C14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" t="s">
-        <v>14</v>
       </c>
       <c r="E14">
         <v>1000</v>
@@ -1143,23 +1165,23 @@
         <f>G14*VLOOKUP(A14,Precios!$A$3:$AA$601,27)</f>
         <v>82200000</v>
       </c>
-      <c r="J14" s="8"/>
+      <c r="J14" s="17"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
-      <c r="M14" s="14">
-        <f t="shared" si="0"/>
-        <v>54000</v>
+      <c r="M14" s="20">
+        <f>M13+K14-L14</f>
+        <v>70000</v>
       </c>
     </row>
     <row r="15" spans="1:22">
-      <c r="A15" s="15">
+      <c r="A15" s="23">
         <v>45669</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
@@ -1182,103 +1204,107 @@
         <f>G15*VLOOKUP(A15,Precios!$A$3:$AA$601,27)</f>
         <v>82200000</v>
       </c>
-      <c r="J15" s="8"/>
+      <c r="J15" s="17"/>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
-      <c r="M15" s="14">
+      <c r="M15" s="20">
         <f t="shared" si="0"/>
-        <v>54000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="15">
-        <v>45698</v>
+      <c r="A16" s="23">
+        <v>45669</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E16">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="F16">
-        <v>64.7</v>
+        <v>68.5</v>
       </c>
       <c r="G16" s="9">
         <f>+F16*E16</f>
-        <v>12940</v>
+        <v>68500</v>
       </c>
       <c r="H16" s="8">
         <f>F16*VLOOKUP(A16,Precios!$A$3:$AA$601,27)</f>
-        <v>78998.7</v>
+        <v>82200</v>
       </c>
       <c r="I16" s="8">
         <f>G16*VLOOKUP(A16,Precios!$A$3:$AA$601,27)</f>
-        <v>15799740</v>
-      </c>
-      <c r="J16" s="8"/>
+        <v>82200000</v>
+      </c>
+      <c r="J16" s="17"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
-      <c r="M16" s="14">
+      <c r="M16" s="20">
         <f t="shared" si="0"/>
-        <v>54000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="17" spans="1:23">
-      <c r="A17" s="15">
-        <v>45846</v>
+      <c r="A17" s="23">
+        <v>45698</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="E17">
+        <v>200</v>
+      </c>
+      <c r="F17">
+        <v>64.7</v>
       </c>
       <c r="G17" s="9">
-        <v>1600</v>
+        <f>+F17*E17</f>
+        <v>12940</v>
       </c>
       <c r="H17" s="8">
         <f>F17*VLOOKUP(A17,Precios!$A$3:$AA$601,27)</f>
-        <v>0</v>
+        <v>78998.7</v>
       </c>
       <c r="I17" s="8">
         <f>G17*VLOOKUP(A17,Precios!$A$3:$AA$601,27)</f>
-        <v>2107200</v>
-      </c>
-      <c r="J17" s="8"/>
+        <v>15799740</v>
+      </c>
+      <c r="J17" s="17"/>
       <c r="K17" s="8"/>
-      <c r="L17" s="8">
+      <c r="L17" s="8"/>
+      <c r="M17" s="20">
+        <f t="shared" si="0"/>
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23">
+      <c r="A18" s="23">
+        <v>45846</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="9">
         <v>1600</v>
-      </c>
-      <c r="M17" s="14">
-        <f t="shared" si="0"/>
-        <v>52400</v>
-      </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="1:23">
-      <c r="A18" s="15">
-        <v>45846</v>
-      </c>
-      <c r="B18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" s="9">
-        <v>75</v>
       </c>
       <c r="H18" s="8">
         <f>F18*VLOOKUP(A18,Precios!$A$3:$AA$601,27)</f>
@@ -1286,354 +1312,424 @@
       </c>
       <c r="I18" s="8">
         <f>G18*VLOOKUP(A18,Precios!$A$3:$AA$601,27)</f>
-        <v>98775</v>
-      </c>
-      <c r="J18" s="8"/>
+        <v>2107200</v>
+      </c>
+      <c r="J18" s="17"/>
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
-      <c r="M18" s="14">
+      <c r="M18" s="20">
         <f t="shared" si="0"/>
-        <v>52400</v>
-      </c>
+        <v>70000</v>
+      </c>
+      <c r="N18" s="3"/>
     </row>
     <row r="19" spans="1:23">
-      <c r="A19" s="15">
+      <c r="A19" s="23">
         <v>45846</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" s="9">
+        <v>15</v>
+      </c>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8">
+        <v>1600</v>
+      </c>
+      <c r="M19" s="20"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="1:23">
+      <c r="A20" s="23">
+        <v>45846</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="9">
+        <v>75</v>
+      </c>
+      <c r="H20" s="8">
+        <f>F20*VLOOKUP(A20,Precios!$A$3:$AA$601,27)</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="8">
+        <f>G20*VLOOKUP(A20,Precios!$A$3:$AA$601,27)</f>
+        <v>98775</v>
+      </c>
+      <c r="J20" s="17"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="20">
+        <f>M18+K20-L20</f>
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23">
+      <c r="A21" s="23">
+        <v>45846</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="9">
         <f>1575/2</f>
         <v>787.5</v>
       </c>
-      <c r="H19" s="8">
-        <f>F19*VLOOKUP(A19,Precios!$A$3:$AA$601,27)</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="8">
-        <f>G19*VLOOKUP(A19,Precios!$A$3:$AA$601,27)</f>
-        <v>1037137.5</v>
-      </c>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="14">
-        <f t="shared" si="0"/>
-        <v>52400</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23">
-      <c r="A20" s="15">
-        <v>45847</v>
-      </c>
-      <c r="B20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20">
-        <v>300</v>
-      </c>
-      <c r="F20">
-        <v>59</v>
-      </c>
-      <c r="G20" s="9">
-        <f>+F20*E20</f>
-        <v>17700</v>
-      </c>
-      <c r="H20" s="8">
-        <f>F20*VLOOKUP(A20,Precios!$A$3:$AA$601,27)</f>
-        <v>77703</v>
-      </c>
-      <c r="I20" s="8">
-        <f>G20*VLOOKUP(A20,Precios!$A$3:$AA$601,27)</f>
-        <v>23310900</v>
-      </c>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="14">
-        <f t="shared" si="0"/>
-        <v>52400</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23">
-      <c r="A21" s="15">
-        <v>45848</v>
-      </c>
-      <c r="B21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21">
-        <v>600</v>
-      </c>
-      <c r="F21">
-        <v>60.7</v>
-      </c>
-      <c r="G21" s="9">
-        <f>+F21*E21</f>
-        <v>36420</v>
-      </c>
       <c r="H21" s="8">
         <f>F21*VLOOKUP(A21,Precios!$A$3:$AA$601,27)</f>
-        <v>80002.600000000006</v>
+        <v>0</v>
       </c>
       <c r="I21" s="8">
         <f>G21*VLOOKUP(A21,Precios!$A$3:$AA$601,27)</f>
-        <v>48001560</v>
-      </c>
-      <c r="J21" s="8"/>
+        <v>1037137.5</v>
+      </c>
+      <c r="J21" s="17"/>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
-      <c r="M21" s="14">
-        <f>M20+K21-L21</f>
-        <v>52400</v>
+      <c r="M21" s="20">
+        <f t="shared" si="0"/>
+        <v>70000</v>
       </c>
     </row>
     <row r="22" spans="1:23">
-      <c r="A22" s="15">
-        <v>45863</v>
-      </c>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
+      <c r="A22" s="23">
+        <v>45847</v>
+      </c>
+      <c r="B22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22">
+        <v>300</v>
+      </c>
+      <c r="F22">
+        <v>59</v>
+      </c>
+      <c r="G22" s="9">
+        <f>+F22*E22</f>
+        <v>17700</v>
+      </c>
+      <c r="H22" s="8">
+        <f>F22*VLOOKUP(A22,Precios!$A$3:$AA$601,27)</f>
+        <v>77703</v>
+      </c>
+      <c r="I22" s="8">
+        <f>G22*VLOOKUP(A22,Precios!$A$3:$AA$601,27)</f>
+        <v>23310900</v>
+      </c>
+      <c r="J22" s="17"/>
       <c r="K22" s="8"/>
-      <c r="L22" s="8">
-        <v>10000</v>
-      </c>
-      <c r="M22" s="14">
-        <f>M21+K22-L22</f>
-        <v>42400</v>
+      <c r="L22" s="8"/>
+      <c r="M22" s="20">
+        <f t="shared" si="0"/>
+        <v>70000</v>
       </c>
     </row>
     <row r="23" spans="1:23">
-      <c r="A23" s="15">
-        <v>45879</v>
+      <c r="A23" s="23">
+        <v>45848</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E23">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="F23">
-        <v>58</v>
+        <v>60.7</v>
       </c>
       <c r="G23" s="9">
         <f>+F23*E23</f>
-        <v>46400</v>
+        <v>36420</v>
       </c>
       <c r="H23" s="8">
         <f>F23*VLOOKUP(A23,Precios!$A$3:$AA$601,27)</f>
-        <v>77662</v>
+        <v>80002.600000000006</v>
       </c>
       <c r="I23" s="8">
         <f>G23*VLOOKUP(A23,Precios!$A$3:$AA$601,27)</f>
-        <v>62129600</v>
-      </c>
-      <c r="J23" s="8"/>
+        <v>48001560</v>
+      </c>
+      <c r="J23" s="17"/>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
-      <c r="M23" s="14">
-        <f t="shared" ref="M23:M27" si="1">M22+K23-L23</f>
-        <v>42400</v>
-      </c>
-      <c r="W23" s="4"/>
+      <c r="M23" s="20">
+        <f>M22+K23-L23</f>
+        <v>70000</v>
+      </c>
     </row>
     <row r="24" spans="1:23">
-      <c r="A24" s="15">
-        <v>45910</v>
+      <c r="A24" s="23">
+        <v>45863</v>
       </c>
       <c r="B24" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8">
+        <v>10000</v>
+      </c>
+      <c r="M24" s="20">
+        <f>M23+K24-L24</f>
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23">
+      <c r="A25" s="23">
+        <v>45879</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" t="s">
         <v>18</v>
       </c>
-      <c r="C24" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24">
-        <v>400</v>
-      </c>
-      <c r="F24">
-        <v>55</v>
-      </c>
-      <c r="G24" s="9">
-        <f>+F24*E24</f>
-        <v>22000</v>
-      </c>
-      <c r="H24" s="8">
-        <f>F24*VLOOKUP(A24,Precios!$A$3:$AA$601,27)</f>
-        <v>74855</v>
-      </c>
-      <c r="I24" s="8">
-        <f>G24*VLOOKUP(A24,Precios!$A$3:$AA$601,27)</f>
-        <v>29942000</v>
-      </c>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="14">
-        <f t="shared" si="1"/>
-        <v>42400</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23">
-      <c r="A25" s="15">
-        <v>45912</v>
-      </c>
-      <c r="B25" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" t="s">
-        <v>21</v>
-      </c>
       <c r="E25">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="F25">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G25" s="9">
         <f>+F25*E25</f>
-        <v>10800</v>
+        <v>46400</v>
       </c>
       <c r="H25" s="8">
         <f>F25*VLOOKUP(A25,Precios!$A$3:$AA$601,27)</f>
-        <v>73602</v>
+        <v>77662</v>
       </c>
       <c r="I25" s="8">
         <f>G25*VLOOKUP(A25,Precios!$A$3:$AA$601,27)</f>
-        <v>14720400</v>
-      </c>
-      <c r="J25" s="8"/>
+        <v>62129600</v>
+      </c>
+      <c r="J25" s="17"/>
       <c r="K25" s="8"/>
-      <c r="L25" s="8">
-        <v>5000</v>
-      </c>
-      <c r="M25" s="14">
-        <f t="shared" si="1"/>
-        <v>37400</v>
-      </c>
+      <c r="L25" s="8"/>
+      <c r="M25" s="20">
+        <f t="shared" ref="M25:M30" si="1">M24+K25-L25</f>
+        <v>60000</v>
+      </c>
+      <c r="W25" s="4"/>
     </row>
     <row r="26" spans="1:23">
-      <c r="A26" s="15">
-        <v>45913</v>
+      <c r="A26" s="23">
+        <v>45910</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D26" t="s">
         <v>22</v>
       </c>
       <c r="E26">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F26">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G26" s="9">
         <f>+F26*E26</f>
-        <v>15000</v>
+        <v>22000</v>
       </c>
       <c r="H26" s="8">
         <f>F26*VLOOKUP(A26,Precios!$A$3:$AA$601,27)</f>
-        <v>68150</v>
+        <v>74855</v>
       </c>
       <c r="I26" s="8">
         <f>G26*VLOOKUP(A26,Precios!$A$3:$AA$601,27)</f>
-        <v>20445000</v>
-      </c>
-      <c r="J26" s="8"/>
+        <v>29942000</v>
+      </c>
+      <c r="J26" s="17"/>
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
-      <c r="M26" s="14">
+      <c r="M26" s="20">
         <f t="shared" si="1"/>
-        <v>37400</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="27" spans="1:23">
-      <c r="A27" s="15">
-        <v>45914</v>
+      <c r="A27" s="23">
+        <v>45912</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D27" t="s">
         <v>22</v>
       </c>
+      <c r="E27">
+        <v>200</v>
+      </c>
+      <c r="F27">
+        <v>54</v>
+      </c>
       <c r="G27" s="9">
-        <v>5000</v>
+        <f>+F27*E27</f>
+        <v>10800</v>
       </c>
       <c r="H27" s="8">
         <f>F27*VLOOKUP(A27,Precios!$A$3:$AA$601,27)</f>
-        <v>0</v>
+        <v>73602</v>
       </c>
       <c r="I27" s="8">
         <f>G27*VLOOKUP(A27,Precios!$A$3:$AA$601,27)</f>
-        <v>6815000</v>
-      </c>
-      <c r="J27" s="8"/>
+        <v>14720400</v>
+      </c>
+      <c r="J27" s="17"/>
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
-      <c r="M27" s="14">
+      <c r="M27" s="20">
         <f t="shared" si="1"/>
-        <v>37400</v>
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23">
+      <c r="A28" s="23">
+        <v>45912</v>
+      </c>
+      <c r="B28" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8">
+        <v>5000</v>
+      </c>
+      <c r="M28" s="20"/>
+    </row>
+    <row r="29" spans="1:23">
+      <c r="A29" s="23">
+        <v>45913</v>
+      </c>
+      <c r="B29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29">
+        <v>300</v>
+      </c>
+      <c r="F29">
+        <v>50</v>
+      </c>
+      <c r="G29" s="9">
+        <f>+F29*E29</f>
+        <v>15000</v>
+      </c>
+      <c r="H29" s="8">
+        <f>F29*VLOOKUP(A29,Precios!$A$3:$AA$601,27)</f>
+        <v>68150</v>
+      </c>
+      <c r="I29" s="8">
+        <f>G29*VLOOKUP(A29,Precios!$A$3:$AA$601,27)</f>
+        <v>20445000</v>
+      </c>
+      <c r="J29" s="17"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="20">
+        <f>M27+K29-L29</f>
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23">
+      <c r="A30" s="23">
+        <v>45914</v>
+      </c>
+      <c r="B30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" s="9">
+        <v>5000</v>
+      </c>
+      <c r="H30" s="8">
+        <f>F30*VLOOKUP(A30,Precios!$A$3:$AA$601,27)</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="8">
+        <f>G30*VLOOKUP(A30,Precios!$A$3:$AA$601,27)</f>
+        <v>6815000</v>
+      </c>
+      <c r="J30" s="17"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="20">
+        <f t="shared" si="1"/>
+        <v>60000</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G27" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G18">
-    <sortCondition ref="A3:A18"/>
+  <autoFilter ref="A1:G30" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G20">
+    <sortCondition ref="A3:A20"/>
   </sortState>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1" xr:uid="{9837364A-ACA4-4040-937F-F0F8B099CD79}">
-      <formula1>$Q$1:$Q$17</formula1>
+      <formula1>$R$1:$R$6</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{5ACDAC43-0A2C-44ED-89F3-6CC7CBBC5473}">
-      <formula1>$S$1:$S$12</formula1>
+      <formula1>$S$1:$S$13</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R4 B14 B3:B12 B16:B38" xr:uid="{D82FC90E-F4C1-4FEE-90A7-1E7B4FF2C652}">
-      <formula1>$Q$1:$Q$24</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R4 B39:B41" xr:uid="{D82FC90E-F4C1-4FEE-90A7-1E7B4FF2C652}">
+      <formula1>$Q$1:$Q$26</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{072F3766-733D-4D00-B107-5AF1B31BCE79}">
-      <formula1>$U$1:$U$36</formula1>
+      <formula1>$U$1:$U$39</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D43" xr:uid="{ED8D13E1-2439-4B9C-AEC1-F990B45E5811}">
-      <formula1>$U$1:$U$58</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D46" xr:uid="{ED8D13E1-2439-4B9C-AEC1-F990B45E5811}">
+      <formula1>$U$1:$U$61</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B38" xr:uid="{544774B8-F57D-4F2D-BFF1-76E0A325DDFD}">
+      <formula1>$R$1:$R$16</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1656,87 +1752,87 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H1" t="s">
         <v>14</v>
       </c>
       <c r="I1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="X1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Y1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Z1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AA1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:28">
       <c r="A2" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B2" s="11">
         <v>60.5</v>

--- a/operaciones.xlsx
+++ b/operaciones.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30002"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7855BA97-534F-4177-9D7C-0E6886B7C8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCCE5A1D-A88D-48EE-9531-124EB904C60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -855,7 +855,7 @@
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
       <c r="M5" s="20">
-        <f t="shared" ref="M5:M22" si="0">M4+K5-L5</f>
+        <f t="shared" ref="M5:M30" si="0">M4+K5-L5</f>
         <v>70000</v>
       </c>
       <c r="O5" s="1"/>
@@ -1060,7 +1060,10 @@
       <c r="L11" s="8">
         <v>16000</v>
       </c>
-      <c r="M11" s="20"/>
+      <c r="M11" s="20">
+        <f t="shared" si="0"/>
+        <v>54000</v>
+      </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="23">
@@ -1090,8 +1093,8 @@
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
       <c r="M12" s="20">
-        <f>M10+K12-L12</f>
-        <v>70000</v>
+        <f t="shared" si="0"/>
+        <v>54000</v>
       </c>
       <c r="O12" s="1"/>
     </row>
@@ -1131,7 +1134,7 @@
       <c r="L13" s="8"/>
       <c r="M13" s="20">
         <f t="shared" si="0"/>
-        <v>70000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1169,8 +1172,8 @@
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
       <c r="M14" s="20">
-        <f>M13+K14-L14</f>
-        <v>70000</v>
+        <f t="shared" si="0"/>
+        <v>54000</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1209,7 +1212,7 @@
       <c r="L15" s="8"/>
       <c r="M15" s="20">
         <f t="shared" si="0"/>
-        <v>70000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1248,7 +1251,7 @@
       <c r="L16" s="8"/>
       <c r="M16" s="20">
         <f t="shared" si="0"/>
-        <v>70000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="17" spans="1:23">
@@ -1287,7 +1290,7 @@
       <c r="L17" s="8"/>
       <c r="M17" s="20">
         <f t="shared" si="0"/>
-        <v>70000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="18" spans="1:23">
@@ -1319,7 +1322,7 @@
       <c r="L18" s="8"/>
       <c r="M18" s="20">
         <f t="shared" si="0"/>
-        <v>70000</v>
+        <v>54000</v>
       </c>
       <c r="N18" s="3"/>
     </row>
@@ -1337,7 +1340,10 @@
       <c r="L19" s="8">
         <v>1600</v>
       </c>
-      <c r="M19" s="20"/>
+      <c r="M19" s="20">
+        <f t="shared" si="0"/>
+        <v>52400</v>
+      </c>
       <c r="N19" s="3"/>
     </row>
     <row r="20" spans="1:23">
@@ -1368,8 +1374,8 @@
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
       <c r="M20" s="20">
-        <f>M18+K20-L20</f>
-        <v>70000</v>
+        <f t="shared" si="0"/>
+        <v>52400</v>
       </c>
     </row>
     <row r="21" spans="1:23">
@@ -1402,7 +1408,7 @@
       <c r="L21" s="8"/>
       <c r="M21" s="20">
         <f t="shared" si="0"/>
-        <v>70000</v>
+        <v>52400</v>
       </c>
     </row>
     <row r="22" spans="1:23">
@@ -1441,7 +1447,7 @@
       <c r="L22" s="8"/>
       <c r="M22" s="20">
         <f t="shared" si="0"/>
-        <v>70000</v>
+        <v>52400</v>
       </c>
     </row>
     <row r="23" spans="1:23">
@@ -1479,8 +1485,8 @@
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
       <c r="M23" s="20">
-        <f>M22+K23-L23</f>
-        <v>70000</v>
+        <f t="shared" si="0"/>
+        <v>52400</v>
       </c>
     </row>
     <row r="24" spans="1:23">
@@ -1498,8 +1504,8 @@
         <v>10000</v>
       </c>
       <c r="M24" s="20">
-        <f>M23+K24-L24</f>
-        <v>60000</v>
+        <f t="shared" si="0"/>
+        <v>42400</v>
       </c>
     </row>
     <row r="25" spans="1:23">
@@ -1537,8 +1543,8 @@
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
       <c r="M25" s="20">
-        <f t="shared" ref="M25:M30" si="1">M24+K25-L25</f>
-        <v>60000</v>
+        <f t="shared" si="0"/>
+        <v>42400</v>
       </c>
       <c r="W25" s="4"/>
     </row>
@@ -1577,8 +1583,8 @@
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
       <c r="M26" s="20">
-        <f t="shared" si="1"/>
-        <v>60000</v>
+        <f t="shared" si="0"/>
+        <v>42400</v>
       </c>
     </row>
     <row r="27" spans="1:23">
@@ -1616,8 +1622,8 @@
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
       <c r="M27" s="20">
-        <f t="shared" si="1"/>
-        <v>60000</v>
+        <f t="shared" si="0"/>
+        <v>42400</v>
       </c>
     </row>
     <row r="28" spans="1:23">
@@ -1634,7 +1640,10 @@
       <c r="L28" s="8">
         <v>5000</v>
       </c>
-      <c r="M28" s="20"/>
+      <c r="M28" s="20">
+        <f t="shared" si="0"/>
+        <v>37400</v>
+      </c>
     </row>
     <row r="29" spans="1:23">
       <c r="A29" s="23">
@@ -1671,8 +1680,8 @@
       <c r="K29" s="8"/>
       <c r="L29" s="8"/>
       <c r="M29" s="20">
-        <f>M27+K29-L29</f>
-        <v>60000</v>
+        <f t="shared" si="0"/>
+        <v>37400</v>
       </c>
     </row>
     <row r="30" spans="1:23">
@@ -1703,8 +1712,8 @@
       <c r="K30" s="8"/>
       <c r="L30" s="8"/>
       <c r="M30" s="20">
-        <f t="shared" si="1"/>
-        <v>60000</v>
+        <f t="shared" si="0"/>
+        <v>37400</v>
       </c>
     </row>
   </sheetData>

--- a/operaciones.xlsx
+++ b/operaciones.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30002"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCCE5A1D-A88D-48EE-9531-124EB904C60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{41D2F06D-80EF-4D75-BA8B-D0D68DA52284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -190,7 +190,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="[$-C0A]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="165" formatCode="[$-C0A]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -292,8 +292,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -708,11 +708,11 @@
         <v>15</v>
       </c>
       <c r="K2">
-        <v>70000</v>
+        <v>150000</v>
       </c>
       <c r="M2" s="19">
         <f>K2-L2</f>
-        <v>70000</v>
+        <v>150000</v>
       </c>
       <c r="N2" s="9"/>
       <c r="O2" s="1"/>
@@ -763,7 +763,7 @@
       <c r="L3" s="8"/>
       <c r="M3" s="20">
         <f>M2+K3-L3</f>
-        <v>70000</v>
+        <v>150000</v>
       </c>
       <c r="N3" s="9"/>
       <c r="O3" s="1"/>
@@ -814,8 +814,9 @@
       <c r="L4" s="8"/>
       <c r="M4" s="20">
         <f>M3+K4-L4</f>
-        <v>70000</v>
-      </c>
+        <v>150000</v>
+      </c>
+      <c r="O4" s="9"/>
       <c r="R4" t="s">
         <v>24</v>
       </c>
@@ -856,7 +857,7 @@
       <c r="L5" s="8"/>
       <c r="M5" s="20">
         <f t="shared" ref="M5:M30" si="0">M4+K5-L5</f>
-        <v>70000</v>
+        <v>150000</v>
       </c>
       <c r="O5" s="1"/>
       <c r="R5" t="s">
@@ -899,7 +900,7 @@
       <c r="L6" s="8"/>
       <c r="M6" s="20">
         <f t="shared" si="0"/>
-        <v>70000</v>
+        <v>150000</v>
       </c>
       <c r="O6" s="1"/>
       <c r="P6" s="9"/>
@@ -940,7 +941,7 @@
       <c r="L7" s="8"/>
       <c r="M7" s="20">
         <f t="shared" si="0"/>
-        <v>70000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -979,7 +980,7 @@
       <c r="L8" s="8"/>
       <c r="M8" s="20">
         <f t="shared" si="0"/>
-        <v>70000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1011,7 +1012,7 @@
       <c r="L9" s="8"/>
       <c r="M9" s="20">
         <f t="shared" si="0"/>
-        <v>70000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1043,7 +1044,7 @@
       <c r="L10" s="8"/>
       <c r="M10" s="20">
         <f t="shared" si="0"/>
-        <v>70000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1062,7 +1063,7 @@
       </c>
       <c r="M11" s="20">
         <f t="shared" si="0"/>
-        <v>54000</v>
+        <v>134000</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1094,7 +1095,7 @@
       <c r="L12" s="8"/>
       <c r="M12" s="20">
         <f t="shared" si="0"/>
-        <v>54000</v>
+        <v>134000</v>
       </c>
       <c r="O12" s="1"/>
     </row>
@@ -1134,7 +1135,7 @@
       <c r="L13" s="8"/>
       <c r="M13" s="20">
         <f t="shared" si="0"/>
-        <v>54000</v>
+        <v>134000</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1173,7 +1174,7 @@
       <c r="L14" s="8"/>
       <c r="M14" s="20">
         <f t="shared" si="0"/>
-        <v>54000</v>
+        <v>134000</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1212,7 +1213,7 @@
       <c r="L15" s="8"/>
       <c r="M15" s="20">
         <f t="shared" si="0"/>
-        <v>54000</v>
+        <v>134000</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1251,7 +1252,7 @@
       <c r="L16" s="8"/>
       <c r="M16" s="20">
         <f t="shared" si="0"/>
-        <v>54000</v>
+        <v>134000</v>
       </c>
     </row>
     <row r="17" spans="1:23">
@@ -1290,7 +1291,7 @@
       <c r="L17" s="8"/>
       <c r="M17" s="20">
         <f t="shared" si="0"/>
-        <v>54000</v>
+        <v>134000</v>
       </c>
     </row>
     <row r="18" spans="1:23">
@@ -1322,7 +1323,7 @@
       <c r="L18" s="8"/>
       <c r="M18" s="20">
         <f t="shared" si="0"/>
-        <v>54000</v>
+        <v>134000</v>
       </c>
       <c r="N18" s="3"/>
     </row>
@@ -1342,7 +1343,7 @@
       </c>
       <c r="M19" s="20">
         <f t="shared" si="0"/>
-        <v>52400</v>
+        <v>132400</v>
       </c>
       <c r="N19" s="3"/>
     </row>
@@ -1375,7 +1376,7 @@
       <c r="L20" s="8"/>
       <c r="M20" s="20">
         <f t="shared" si="0"/>
-        <v>52400</v>
+        <v>132400</v>
       </c>
     </row>
     <row r="21" spans="1:23">
@@ -1408,7 +1409,7 @@
       <c r="L21" s="8"/>
       <c r="M21" s="20">
         <f t="shared" si="0"/>
-        <v>52400</v>
+        <v>132400</v>
       </c>
     </row>
     <row r="22" spans="1:23">
@@ -1447,7 +1448,7 @@
       <c r="L22" s="8"/>
       <c r="M22" s="20">
         <f t="shared" si="0"/>
-        <v>52400</v>
+        <v>132400</v>
       </c>
     </row>
     <row r="23" spans="1:23">
@@ -1486,7 +1487,7 @@
       <c r="L23" s="8"/>
       <c r="M23" s="20">
         <f t="shared" si="0"/>
-        <v>52400</v>
+        <v>132400</v>
       </c>
     </row>
     <row r="24" spans="1:23">
@@ -1505,7 +1506,7 @@
       </c>
       <c r="M24" s="20">
         <f t="shared" si="0"/>
-        <v>42400</v>
+        <v>122400</v>
       </c>
     </row>
     <row r="25" spans="1:23">
@@ -1544,7 +1545,7 @@
       <c r="L25" s="8"/>
       <c r="M25" s="20">
         <f t="shared" si="0"/>
-        <v>42400</v>
+        <v>122400</v>
       </c>
       <c r="W25" s="4"/>
     </row>
@@ -1584,7 +1585,7 @@
       <c r="L26" s="8"/>
       <c r="M26" s="20">
         <f t="shared" si="0"/>
-        <v>42400</v>
+        <v>122400</v>
       </c>
     </row>
     <row r="27" spans="1:23">
@@ -1623,7 +1624,7 @@
       <c r="L27" s="8"/>
       <c r="M27" s="20">
         <f t="shared" si="0"/>
-        <v>42400</v>
+        <v>122400</v>
       </c>
     </row>
     <row r="28" spans="1:23">
@@ -1642,7 +1643,7 @@
       </c>
       <c r="M28" s="20">
         <f t="shared" si="0"/>
-        <v>37400</v>
+        <v>117400</v>
       </c>
     </row>
     <row r="29" spans="1:23">
@@ -1681,7 +1682,7 @@
       <c r="L29" s="8"/>
       <c r="M29" s="20">
         <f t="shared" si="0"/>
-        <v>37400</v>
+        <v>117400</v>
       </c>
     </row>
     <row r="30" spans="1:23">
@@ -1713,7 +1714,7 @@
       <c r="L30" s="8"/>
       <c r="M30" s="20">
         <f t="shared" si="0"/>
-        <v>37400</v>
+        <v>117400</v>
       </c>
     </row>
   </sheetData>
